--- a/VerveStacks_ITA_grids_syn_5/vt_vervestacks_ITA_v1.xlsx
+++ b/VerveStacks_ITA_grids_syn_5/vt_vervestacks_ITA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids_syn_5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{20BB4251-2C48-479C-A792-ED7B5E01285D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{578732B1-3B90-40BA-8427-D6262BABA8CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{32EDD261-F4BB-476A-8547-BAD89B16BD5A}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{AE05CA47-5B9F-4601-9462-9953F0A10C4A}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -3673,7 +3673,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F44AB39A-8D51-411F-8730-0C9E257A6106}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5084EAA3-681C-4254-95F9-B8D6D567783B}">
   <dimension ref="B9:T165"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4424,7 +4424,7 @@
         <v>14</v>
       </c>
       <c r="E23">
-        <v>8.5589832000000018E-2</v>
+        <v>0.11076331200000004</v>
       </c>
       <c r="F23">
         <v>3583</v>
@@ -4480,7 +4480,7 @@
         <v>18</v>
       </c>
       <c r="E24">
-        <v>8.5589832000000018E-2</v>
+        <v>0.11076331200000004</v>
       </c>
       <c r="F24">
         <v>3583</v>
@@ -4536,7 +4536,7 @@
         <v>26</v>
       </c>
       <c r="E25">
-        <v>8.5589832000000018E-2</v>
+        <v>0.11076331200000002</v>
       </c>
       <c r="F25">
         <v>3583</v>
@@ -4592,19 +4592,19 @@
         <v>26</v>
       </c>
       <c r="E26">
-        <v>0.12764790000000001</v>
+        <v>0.20149272000000007</v>
       </c>
       <c r="F26">
-        <v>3144</v>
+        <v>2757</v>
       </c>
       <c r="G26">
-        <v>43.8</v>
+        <v>39.200000000000003</v>
       </c>
       <c r="H26">
-        <v>3.94</v>
+        <v>3.35</v>
       </c>
       <c r="I26">
-        <v>0.59565000000000001</v>
+        <v>0.63080000000000003</v>
       </c>
       <c r="J26" t="s">
         <v>33</v>
@@ -4648,19 +4648,19 @@
         <v>26</v>
       </c>
       <c r="E27">
-        <v>0.12764790000000001</v>
+        <v>0.20149272000000007</v>
       </c>
       <c r="F27">
-        <v>3144</v>
+        <v>2757</v>
       </c>
       <c r="G27">
-        <v>43.8</v>
+        <v>39.200000000000003</v>
       </c>
       <c r="H27">
-        <v>3.94</v>
+        <v>3.35</v>
       </c>
       <c r="I27">
-        <v>0.59565000000000001</v>
+        <v>0.63080000000000003</v>
       </c>
       <c r="J27" t="s">
         <v>34</v>
@@ -4704,19 +4704,19 @@
         <v>26</v>
       </c>
       <c r="E28">
-        <v>0.12764790000000001</v>
+        <v>0.20149272000000007</v>
       </c>
       <c r="F28">
-        <v>3144</v>
+        <v>2757</v>
       </c>
       <c r="G28">
-        <v>43.8</v>
+        <v>39.200000000000003</v>
       </c>
       <c r="H28">
-        <v>3.94</v>
+        <v>3.35</v>
       </c>
       <c r="I28">
-        <v>0.59565000000000001</v>
+        <v>0.63080000000000003</v>
       </c>
       <c r="J28" t="s">
         <v>35</v>
@@ -4760,19 +4760,19 @@
         <v>26</v>
       </c>
       <c r="E29">
-        <v>8.7830160000000032E-2</v>
+        <v>0.18470166000000002</v>
       </c>
       <c r="F29">
-        <v>3583</v>
+        <v>2757</v>
       </c>
       <c r="G29">
-        <v>49</v>
+        <v>39.200000000000003</v>
       </c>
       <c r="H29">
-        <v>4.59</v>
+        <v>3.35</v>
       </c>
       <c r="I29">
-        <v>0.5605</v>
+        <v>0.63080000000000003</v>
       </c>
       <c r="J29" t="s">
         <v>36</v>
@@ -4816,7 +4816,7 @@
         <v>14</v>
       </c>
       <c r="E30">
-        <v>0.260522535</v>
+        <v>0.33714680999999996</v>
       </c>
       <c r="F30">
         <v>1967</v>
@@ -4872,7 +4872,7 @@
         <v>14</v>
       </c>
       <c r="E31">
-        <v>0.260522535</v>
+        <v>0.33714680999999996</v>
       </c>
       <c r="F31">
         <v>1967</v>
@@ -4928,7 +4928,7 @@
         <v>14</v>
       </c>
       <c r="E32">
-        <v>0.260522535</v>
+        <v>0.33714680999999996</v>
       </c>
       <c r="F32">
         <v>1967</v>
@@ -4984,7 +4984,7 @@
         <v>18</v>
       </c>
       <c r="E33">
-        <v>0.28056272999999998</v>
+        <v>0.36308118</v>
       </c>
       <c r="F33">
         <v>1967</v>
@@ -5040,7 +5040,7 @@
         <v>18</v>
       </c>
       <c r="E34">
-        <v>0.28056272999999998</v>
+        <v>0.36308118</v>
       </c>
       <c r="F34">
         <v>1967</v>
@@ -5096,7 +5096,7 @@
         <v>18</v>
       </c>
       <c r="E35">
-        <v>0.28056272999999998</v>
+        <v>0.36308118</v>
       </c>
       <c r="F35">
         <v>1967</v>
@@ -5152,7 +5152,7 @@
         <v>14</v>
       </c>
       <c r="E36">
-        <v>0.41750406250000005</v>
+        <v>0.53047575000000013</v>
       </c>
       <c r="F36">
         <v>1365</v>
@@ -5208,7 +5208,7 @@
         <v>18</v>
       </c>
       <c r="E37">
-        <v>0.44431624999999997</v>
+        <v>0.56454300000000002</v>
       </c>
       <c r="F37">
         <v>1365</v>
@@ -5264,7 +5264,7 @@
         <v>18</v>
       </c>
       <c r="E38">
-        <v>0.38303124999999993</v>
+        <v>0.48667500000000002</v>
       </c>
       <c r="F38">
         <v>1365</v>
@@ -5320,7 +5320,7 @@
         <v>16</v>
       </c>
       <c r="E39">
-        <v>0.44431624999999997</v>
+        <v>0.56454300000000002</v>
       </c>
       <c r="F39">
         <v>1365</v>
@@ -5376,7 +5376,7 @@
         <v>14</v>
       </c>
       <c r="E40">
-        <v>0.41750406249999999</v>
+        <v>0.53047575000000013</v>
       </c>
       <c r="F40">
         <v>1365</v>
@@ -5432,7 +5432,7 @@
         <v>14</v>
       </c>
       <c r="E41">
-        <v>0.41750406249999999</v>
+        <v>0.53047575000000013</v>
       </c>
       <c r="F41">
         <v>1365</v>
@@ -5488,7 +5488,7 @@
         <v>14</v>
       </c>
       <c r="E42">
-        <v>0.41750406249999999</v>
+        <v>0.53047575000000013</v>
       </c>
       <c r="F42">
         <v>1365</v>
@@ -5544,7 +5544,7 @@
         <v>14</v>
       </c>
       <c r="E43">
-        <v>0.41750406249999999</v>
+        <v>0.53047575000000013</v>
       </c>
       <c r="F43">
         <v>1365</v>
@@ -5600,7 +5600,7 @@
         <v>16</v>
       </c>
       <c r="E44">
-        <v>0.41750406249999999</v>
+        <v>0.53047575000000013</v>
       </c>
       <c r="F44">
         <v>1365</v>
@@ -5656,7 +5656,7 @@
         <v>14</v>
       </c>
       <c r="E45">
-        <v>0.40218281250000004</v>
+        <v>0.51100875000000012</v>
       </c>
       <c r="F45">
         <v>1365</v>
@@ -5712,7 +5712,7 @@
         <v>16</v>
       </c>
       <c r="E46">
-        <v>0.41750406249999999</v>
+        <v>0.53047575000000013</v>
       </c>
       <c r="F46">
         <v>1365</v>
@@ -5768,7 +5768,7 @@
         <v>16</v>
       </c>
       <c r="E47">
-        <v>0.41750406249999999</v>
+        <v>0.53047575000000013</v>
       </c>
       <c r="F47">
         <v>1365</v>
@@ -5824,7 +5824,7 @@
         <v>16</v>
       </c>
       <c r="E48">
-        <v>0.41750406249999999</v>
+        <v>0.53047575000000013</v>
       </c>
       <c r="F48">
         <v>1365</v>
@@ -5880,7 +5880,7 @@
         <v>16</v>
       </c>
       <c r="E49">
-        <v>0.41750406249999999</v>
+        <v>0.53047575000000013</v>
       </c>
       <c r="F49">
         <v>1365</v>
@@ -5936,7 +5936,7 @@
         <v>16</v>
       </c>
       <c r="E50">
-        <v>0.3983525</v>
+        <v>0.50614200000000009</v>
       </c>
       <c r="F50">
         <v>1365</v>
@@ -5992,7 +5992,7 @@
         <v>16</v>
       </c>
       <c r="E51">
-        <v>0.41750406249999999</v>
+        <v>0.53047575000000013</v>
       </c>
       <c r="F51">
         <v>1365</v>
@@ -6048,7 +6048,7 @@
         <v>16</v>
       </c>
       <c r="E52">
-        <v>0.41750406249999999</v>
+        <v>0.53047575000000013</v>
       </c>
       <c r="F52">
         <v>1365</v>
@@ -6104,7 +6104,7 @@
         <v>14</v>
       </c>
       <c r="E53">
-        <v>0.41750406249999999</v>
+        <v>0.53047575000000013</v>
       </c>
       <c r="F53">
         <v>1365</v>
@@ -6160,7 +6160,7 @@
         <v>14</v>
       </c>
       <c r="E54">
-        <v>0.41750406249999999</v>
+        <v>0.53047575000000013</v>
       </c>
       <c r="F54">
         <v>1365</v>
@@ -6216,7 +6216,7 @@
         <v>16</v>
       </c>
       <c r="E55">
-        <v>0.41750406249999999</v>
+        <v>0.53047575000000013</v>
       </c>
       <c r="F55">
         <v>1365</v>
@@ -6272,7 +6272,7 @@
         <v>16</v>
       </c>
       <c r="E56">
-        <v>0.41750406249999999</v>
+        <v>0.53047575000000013</v>
       </c>
       <c r="F56">
         <v>1365</v>
@@ -6328,7 +6328,7 @@
         <v>16</v>
       </c>
       <c r="E57">
-        <v>0.41750406249999999</v>
+        <v>0.53047575000000013</v>
       </c>
       <c r="F57">
         <v>1365</v>
@@ -6384,7 +6384,7 @@
         <v>16</v>
       </c>
       <c r="E58">
-        <v>0.41750406249999999</v>
+        <v>0.53047575000000013</v>
       </c>
       <c r="F58">
         <v>1365</v>
@@ -6440,7 +6440,7 @@
         <v>16</v>
       </c>
       <c r="E59">
-        <v>0.40218281250000004</v>
+        <v>0.51100875000000012</v>
       </c>
       <c r="F59">
         <v>1365</v>
@@ -6496,7 +6496,7 @@
         <v>16</v>
       </c>
       <c r="E60">
-        <v>0.40218281250000004</v>
+        <v>0.51100875000000012</v>
       </c>
       <c r="F60">
         <v>1365</v>
@@ -6552,7 +6552,7 @@
         <v>16</v>
       </c>
       <c r="E61">
-        <v>0.41750406249999999</v>
+        <v>0.53047575000000013</v>
       </c>
       <c r="F61">
         <v>1365</v>
@@ -6608,7 +6608,7 @@
         <v>18</v>
       </c>
       <c r="E62">
-        <v>0.45963749999999998</v>
+        <v>0.58401000000000003</v>
       </c>
       <c r="F62">
         <v>1365</v>
@@ -6664,7 +6664,7 @@
         <v>18</v>
       </c>
       <c r="E63">
-        <v>0.41750406249999999</v>
+        <v>0.53047575000000013</v>
       </c>
       <c r="F63">
         <v>1365</v>
@@ -6720,7 +6720,7 @@
         <v>73</v>
       </c>
       <c r="E64">
-        <v>0.38303124999999993</v>
+        <v>0.48667500000000002</v>
       </c>
       <c r="F64">
         <v>1365</v>
@@ -6776,7 +6776,7 @@
         <v>14</v>
       </c>
       <c r="E65">
-        <v>0.41750406249999999</v>
+        <v>0.53047575000000013</v>
       </c>
       <c r="F65">
         <v>1365</v>
@@ -6832,7 +6832,7 @@
         <v>16</v>
       </c>
       <c r="E66">
-        <v>0.41750406249999999</v>
+        <v>0.53047575000000013</v>
       </c>
       <c r="F66">
         <v>1365</v>
@@ -6888,7 +6888,7 @@
         <v>16</v>
       </c>
       <c r="E67">
-        <v>0.41750406249999999</v>
+        <v>0.53047575000000013</v>
       </c>
       <c r="F67">
         <v>1365</v>
@@ -6944,7 +6944,7 @@
         <v>18</v>
       </c>
       <c r="E68">
-        <v>0.40218281249999999</v>
+        <v>0.51100875000000012</v>
       </c>
       <c r="F68">
         <v>1365</v>
@@ -7000,7 +7000,7 @@
         <v>18</v>
       </c>
       <c r="E69">
-        <v>0.40218281249999999</v>
+        <v>0.51100875000000012</v>
       </c>
       <c r="F69">
         <v>1365</v>
@@ -7056,7 +7056,7 @@
         <v>18</v>
       </c>
       <c r="E70">
-        <v>0.38303124999999993</v>
+        <v>0.48667500000000002</v>
       </c>
       <c r="F70">
         <v>1365</v>
@@ -7112,7 +7112,7 @@
         <v>18</v>
       </c>
       <c r="E71">
-        <v>0.38303124999999993</v>
+        <v>0.48667500000000002</v>
       </c>
       <c r="F71">
         <v>1365</v>
@@ -7168,7 +7168,7 @@
         <v>14</v>
       </c>
       <c r="E72">
-        <v>0.41750406249999999</v>
+        <v>0.53047575000000013</v>
       </c>
       <c r="F72">
         <v>1365</v>
@@ -7224,7 +7224,7 @@
         <v>73</v>
       </c>
       <c r="E73">
-        <v>0.41750406249999999</v>
+        <v>0.53047575000000013</v>
       </c>
       <c r="F73">
         <v>1365</v>
@@ -7280,7 +7280,7 @@
         <v>16</v>
       </c>
       <c r="E74">
-        <v>0.41750406249999999</v>
+        <v>0.53047575000000013</v>
       </c>
       <c r="F74">
         <v>1365</v>
@@ -7336,7 +7336,7 @@
         <v>16</v>
       </c>
       <c r="E75">
-        <v>0.41750406249999999</v>
+        <v>0.53047575000000013</v>
       </c>
       <c r="F75">
         <v>1365</v>
@@ -7392,7 +7392,7 @@
         <v>16</v>
       </c>
       <c r="E76">
-        <v>0.41750406249999999</v>
+        <v>0.53047575000000013</v>
       </c>
       <c r="F76">
         <v>1365</v>
@@ -7448,7 +7448,7 @@
         <v>18</v>
       </c>
       <c r="E77">
-        <v>0.41750406249999999</v>
+        <v>0.53047575000000013</v>
       </c>
       <c r="F77">
         <v>1365</v>
@@ -7504,7 +7504,7 @@
         <v>16</v>
       </c>
       <c r="E78">
-        <v>0.34472812500000005</v>
+        <v>0.43800749999999999</v>
       </c>
       <c r="F78">
         <v>1365</v>
@@ -7560,7 +7560,7 @@
         <v>18</v>
       </c>
       <c r="E79">
-        <v>0.41750406249999999</v>
+        <v>0.53047575000000013</v>
       </c>
       <c r="F79">
         <v>1365</v>
@@ -7616,7 +7616,7 @@
         <v>18</v>
       </c>
       <c r="E80">
-        <v>0.41750406249999999</v>
+        <v>0.53047575000000013</v>
       </c>
       <c r="F80">
         <v>1365</v>
@@ -7672,7 +7672,7 @@
         <v>73</v>
       </c>
       <c r="E81">
-        <v>0.41750406249999999</v>
+        <v>0.53047575000000013</v>
       </c>
       <c r="F81">
         <v>1365</v>
@@ -7728,7 +7728,7 @@
         <v>73</v>
       </c>
       <c r="E82">
-        <v>0.41750406249999999</v>
+        <v>0.53047575000000013</v>
       </c>
       <c r="F82">
         <v>1365</v>
@@ -7784,7 +7784,7 @@
         <v>73</v>
       </c>
       <c r="E83">
-        <v>0.41750406249999999</v>
+        <v>0.53047575000000013</v>
       </c>
       <c r="F83">
         <v>1365</v>
@@ -7840,7 +7840,7 @@
         <v>73</v>
       </c>
       <c r="E84">
-        <v>0.41750406249999999</v>
+        <v>0.53047575000000013</v>
       </c>
       <c r="F84">
         <v>1365</v>
@@ -7896,7 +7896,7 @@
         <v>18</v>
       </c>
       <c r="E85">
-        <v>0.42899500000000002</v>
+        <v>0.54507600000000023</v>
       </c>
       <c r="F85">
         <v>1365</v>
@@ -7952,7 +7952,7 @@
         <v>18</v>
       </c>
       <c r="E86">
-        <v>0.41750406249999999</v>
+        <v>0.53047575000000013</v>
       </c>
       <c r="F86">
         <v>1365</v>
@@ -8008,7 +8008,7 @@
         <v>18</v>
       </c>
       <c r="E87">
-        <v>0.41750406249999999</v>
+        <v>0.53047575000000013</v>
       </c>
       <c r="F87">
         <v>1365</v>
@@ -8064,7 +8064,7 @@
         <v>14</v>
       </c>
       <c r="E88">
-        <v>0.44431624999999997</v>
+        <v>0.56454300000000002</v>
       </c>
       <c r="F88">
         <v>1365</v>
@@ -8120,7 +8120,7 @@
         <v>18</v>
       </c>
       <c r="E89">
-        <v>0.41750406249999999</v>
+        <v>0.53047575000000013</v>
       </c>
       <c r="F89">
         <v>1365</v>
@@ -8176,7 +8176,7 @@
         <v>14</v>
       </c>
       <c r="E90">
-        <v>0.41750406249999999</v>
+        <v>0.53047575000000013</v>
       </c>
       <c r="F90">
         <v>1365</v>
@@ -8232,7 +8232,7 @@
         <v>14</v>
       </c>
       <c r="E91">
-        <v>0.41750406249999999</v>
+        <v>0.53047575000000013</v>
       </c>
       <c r="F91">
         <v>1365</v>
@@ -8288,7 +8288,7 @@
         <v>16</v>
       </c>
       <c r="E92">
-        <v>0.41750406249999999</v>
+        <v>0.53047575000000013</v>
       </c>
       <c r="F92">
         <v>1365</v>
@@ -8344,7 +8344,7 @@
         <v>16</v>
       </c>
       <c r="E93">
-        <v>0.41750406249999999</v>
+        <v>0.53047575000000013</v>
       </c>
       <c r="F93">
         <v>1365</v>
@@ -8400,7 +8400,7 @@
         <v>14</v>
       </c>
       <c r="E94">
-        <v>0.41750406249999999</v>
+        <v>0.53047575000000013</v>
       </c>
       <c r="F94">
         <v>1365</v>
@@ -8456,7 +8456,7 @@
         <v>14</v>
       </c>
       <c r="E95">
-        <v>0.41750406249999999</v>
+        <v>0.53047575000000013</v>
       </c>
       <c r="F95">
         <v>1365</v>
@@ -8512,7 +8512,7 @@
         <v>14</v>
       </c>
       <c r="E96">
-        <v>0.41750406249999999</v>
+        <v>0.53047575000000013</v>
       </c>
       <c r="F96">
         <v>1365</v>
@@ -8568,7 +8568,7 @@
         <v>16</v>
       </c>
       <c r="E97">
-        <v>0.41750406249999999</v>
+        <v>0.53047575000000013</v>
       </c>
       <c r="F97">
         <v>1365</v>
@@ -8624,7 +8624,7 @@
         <v>16</v>
       </c>
       <c r="E98">
-        <v>0.41750406249999999</v>
+        <v>0.53047575000000013</v>
       </c>
       <c r="F98">
         <v>1365</v>
@@ -8680,7 +8680,7 @@
         <v>73</v>
       </c>
       <c r="E99">
-        <v>0.41750406249999999</v>
+        <v>0.53047575000000013</v>
       </c>
       <c r="F99">
         <v>1365</v>
@@ -8736,7 +8736,7 @@
         <v>14</v>
       </c>
       <c r="E100">
-        <v>0.41750406249999999</v>
+        <v>0.53047575000000013</v>
       </c>
       <c r="F100">
         <v>1365</v>
@@ -8792,7 +8792,7 @@
         <v>16</v>
       </c>
       <c r="E101">
-        <v>0.44431624999999997</v>
+        <v>0.56454300000000002</v>
       </c>
       <c r="F101">
         <v>1365</v>
@@ -8848,7 +8848,7 @@
         <v>18</v>
       </c>
       <c r="E102">
-        <v>0.41750406249999999</v>
+        <v>0.53047575000000013</v>
       </c>
       <c r="F102">
         <v>1365</v>
@@ -8904,7 +8904,7 @@
         <v>18</v>
       </c>
       <c r="E103">
-        <v>0.41750406249999999</v>
+        <v>0.53047575000000013</v>
       </c>
       <c r="F103">
         <v>1365</v>
@@ -8960,7 +8960,7 @@
         <v>18</v>
       </c>
       <c r="E104">
-        <v>0.41750406249999999</v>
+        <v>0.53047575000000013</v>
       </c>
       <c r="F104">
         <v>1365</v>
@@ -9016,7 +9016,7 @@
         <v>16</v>
       </c>
       <c r="E105">
-        <v>0.41750406249999999</v>
+        <v>0.53047574999999991</v>
       </c>
       <c r="F105">
         <v>1365</v>
@@ -9072,7 +9072,7 @@
         <v>16</v>
       </c>
       <c r="E106">
-        <v>0.41750406249999999</v>
+        <v>0.53047575000000013</v>
       </c>
       <c r="F106">
         <v>1365</v>
@@ -9128,7 +9128,7 @@
         <v>16</v>
       </c>
       <c r="E107">
-        <v>0.41750406249999999</v>
+        <v>0.53047575000000013</v>
       </c>
       <c r="F107">
         <v>1365</v>
@@ -9184,7 +9184,7 @@
         <v>14</v>
       </c>
       <c r="E108">
-        <v>0.45963749999999998</v>
+        <v>0.58401000000000003</v>
       </c>
       <c r="F108">
         <v>1365</v>
@@ -9240,7 +9240,7 @@
         <v>18</v>
       </c>
       <c r="E109">
-        <v>0.45963749999999998</v>
+        <v>0.58401000000000003</v>
       </c>
       <c r="F109">
         <v>1365</v>
@@ -9296,7 +9296,7 @@
         <v>16</v>
       </c>
       <c r="E110">
-        <v>0.45963749999999998</v>
+        <v>0.58401000000000003</v>
       </c>
       <c r="F110">
         <v>1365</v>
@@ -9352,7 +9352,7 @@
         <v>18</v>
       </c>
       <c r="E111">
-        <v>0.41750406249999999</v>
+        <v>0.53047575000000013</v>
       </c>
       <c r="F111">
         <v>1365</v>
@@ -9408,7 +9408,7 @@
         <v>18</v>
       </c>
       <c r="E112">
-        <v>0.41750406249999999</v>
+        <v>0.53047575000000013</v>
       </c>
       <c r="F112">
         <v>1365</v>
@@ -9464,7 +9464,7 @@
         <v>16</v>
       </c>
       <c r="E113">
-        <v>0.41750406249999999</v>
+        <v>0.53047575000000013</v>
       </c>
       <c r="F113">
         <v>1365</v>
@@ -9520,7 +9520,7 @@
         <v>16</v>
       </c>
       <c r="E114">
-        <v>0.41750406249999999</v>
+        <v>0.53047575000000013</v>
       </c>
       <c r="F114">
         <v>1365</v>
@@ -9576,7 +9576,7 @@
         <v>73</v>
       </c>
       <c r="E115">
-        <v>0.38303124999999993</v>
+        <v>0.48667500000000002</v>
       </c>
       <c r="F115">
         <v>1365</v>
@@ -9632,7 +9632,7 @@
         <v>73</v>
       </c>
       <c r="E116">
-        <v>0.38303124999999993</v>
+        <v>0.48667500000000002</v>
       </c>
       <c r="F116">
         <v>1365</v>
@@ -9688,7 +9688,7 @@
         <v>14</v>
       </c>
       <c r="E117">
-        <v>0.4021828125000001</v>
+        <v>0.51100875000000012</v>
       </c>
       <c r="F117">
         <v>1365</v>
@@ -9744,7 +9744,7 @@
         <v>18</v>
       </c>
       <c r="E118">
-        <v>0.38303124999999993</v>
+        <v>0.48667500000000002</v>
       </c>
       <c r="F118">
         <v>1365</v>
@@ -9800,7 +9800,7 @@
         <v>26</v>
       </c>
       <c r="E119">
-        <v>0.41750406249999999</v>
+        <v>0.53047575000000013</v>
       </c>
       <c r="F119">
         <v>1365</v>
@@ -9856,7 +9856,7 @@
         <v>16</v>
       </c>
       <c r="E120">
-        <v>0.3983525</v>
+        <v>0.50614200000000009</v>
       </c>
       <c r="F120">
         <v>1365</v>
@@ -9912,7 +9912,7 @@
         <v>18</v>
       </c>
       <c r="E121">
-        <v>0.3983525</v>
+        <v>0.50614200000000009</v>
       </c>
       <c r="F121">
         <v>1365</v>
@@ -9968,7 +9968,7 @@
         <v>18</v>
       </c>
       <c r="E122">
-        <v>0.41750406249999999</v>
+        <v>0.53047575000000013</v>
       </c>
       <c r="F122">
         <v>1365</v>
@@ -10024,7 +10024,7 @@
         <v>14</v>
       </c>
       <c r="E123">
-        <v>0.41367375000000001</v>
+        <v>0.5256090000000001</v>
       </c>
       <c r="F123">
         <v>1365</v>
@@ -10080,7 +10080,7 @@
         <v>18</v>
       </c>
       <c r="E124">
-        <v>0.42899500000000002</v>
+        <v>0.54507600000000023</v>
       </c>
       <c r="F124">
         <v>1365</v>
@@ -10136,7 +10136,7 @@
         <v>73</v>
       </c>
       <c r="E125">
-        <v>0.41367375000000001</v>
+        <v>0.5256090000000001</v>
       </c>
       <c r="F125">
         <v>1365</v>
@@ -10192,7 +10192,7 @@
         <v>16</v>
       </c>
       <c r="E126">
-        <v>0.42899500000000002</v>
+        <v>0.54507600000000023</v>
       </c>
       <c r="F126">
         <v>1365</v>
@@ -10248,7 +10248,7 @@
         <v>16</v>
       </c>
       <c r="E127">
-        <v>0.25280062500000006</v>
+        <v>0.32120550000000009</v>
       </c>
       <c r="F127">
         <v>1365</v>
@@ -10304,7 +10304,7 @@
         <v>73</v>
       </c>
       <c r="E128">
-        <v>0.24514000000000002</v>
+        <v>0.31147200000000003</v>
       </c>
       <c r="F128">
         <v>1365</v>
@@ -10360,7 +10360,7 @@
         <v>73</v>
       </c>
       <c r="E129">
-        <v>0.24514000000000002</v>
+        <v>0.31147200000000003</v>
       </c>
       <c r="F129">
         <v>1365</v>
@@ -10416,7 +10416,7 @@
         <v>18</v>
       </c>
       <c r="E130">
-        <v>0.21066718750000002</v>
+        <v>0.26767125000000008</v>
       </c>
       <c r="F130">
         <v>1365</v>
@@ -10472,7 +10472,7 @@
         <v>14</v>
       </c>
       <c r="E131">
-        <v>0.21449749999999998</v>
+        <v>0.27253800000000011</v>
       </c>
       <c r="F131">
         <v>1365</v>
@@ -10528,7 +10528,7 @@
         <v>73</v>
       </c>
       <c r="E132">
-        <v>0.23747937499999999</v>
+        <v>0.30173850000000008</v>
       </c>
       <c r="F132">
         <v>1365</v>
@@ -10584,7 +10584,7 @@
         <v>16</v>
       </c>
       <c r="E133">
-        <v>0.22981874999999999</v>
+        <v>0.29200500000000001</v>
       </c>
       <c r="F133">
         <v>1365</v>
@@ -10640,7 +10640,7 @@
         <v>14</v>
       </c>
       <c r="E134">
-        <v>0.2463523125</v>
+        <v>0.31301235000000005</v>
       </c>
       <c r="F134">
         <v>1365</v>
@@ -10696,7 +10696,7 @@
         <v>18</v>
       </c>
       <c r="E135">
-        <v>0.2463523125</v>
+        <v>0.31301235000000005</v>
       </c>
       <c r="F135">
         <v>1365</v>
@@ -10752,7 +10752,7 @@
         <v>73</v>
       </c>
       <c r="E136">
-        <v>0.2463523125</v>
+        <v>0.31301235000000005</v>
       </c>
       <c r="F136">
         <v>1365</v>
@@ -10808,7 +10808,7 @@
         <v>26</v>
       </c>
       <c r="E137">
-        <v>0.2463523125</v>
+        <v>0.31301235000000005</v>
       </c>
       <c r="F137">
         <v>1365</v>
@@ -10864,7 +10864,7 @@
         <v>16</v>
       </c>
       <c r="E138">
-        <v>0.2463523125</v>
+        <v>0.31301235000000005</v>
       </c>
       <c r="F138">
         <v>1365</v>
@@ -10920,7 +10920,7 @@
         <v>14</v>
       </c>
       <c r="E139">
-        <v>0.27578249999999999</v>
+        <v>0.35040600000000005</v>
       </c>
       <c r="F139">
         <v>1365</v>
@@ -10976,7 +10976,7 @@
         <v>18</v>
       </c>
       <c r="E140">
-        <v>0.27578249999999999</v>
+        <v>0.35040600000000005</v>
       </c>
       <c r="F140">
         <v>1365</v>
@@ -11032,7 +11032,7 @@
         <v>16</v>
       </c>
       <c r="E141">
-        <v>0.27578249999999999</v>
+        <v>0.35040600000000005</v>
       </c>
       <c r="F141">
         <v>1365</v>
@@ -11062,7 +11062,7 @@
         <v>935</v>
       </c>
       <c r="P141" t="s">
-        <v>1077</v>
+        <v>1067</v>
       </c>
       <c r="Q141" t="s">
         <v>389</v>
@@ -11088,7 +11088,7 @@
         <v>14</v>
       </c>
       <c r="E142">
-        <v>0.23747937499999999</v>
+        <v>0.30173850000000008</v>
       </c>
       <c r="F142">
         <v>1365</v>
@@ -11118,7 +11118,7 @@
         <v>935</v>
       </c>
       <c r="P142" t="s">
-        <v>1067</v>
+        <v>1077</v>
       </c>
       <c r="Q142" t="s">
         <v>389</v>
@@ -11144,7 +11144,7 @@
         <v>14</v>
       </c>
       <c r="E143">
-        <v>0.23747937499999999</v>
+        <v>0.30173850000000008</v>
       </c>
       <c r="F143">
         <v>1365</v>
@@ -11200,7 +11200,7 @@
         <v>14</v>
       </c>
       <c r="E144">
-        <v>0.23747937499999999</v>
+        <v>0.30173850000000008</v>
       </c>
       <c r="F144">
         <v>1365</v>
@@ -11256,7 +11256,7 @@
         <v>14</v>
       </c>
       <c r="E145">
-        <v>0.23747937499999999</v>
+        <v>0.30173850000000008</v>
       </c>
       <c r="F145">
         <v>1365</v>
@@ -11312,7 +11312,7 @@
         <v>18</v>
       </c>
       <c r="E146">
-        <v>0.25663093749999999</v>
+        <v>0.32607225000000006</v>
       </c>
       <c r="F146">
         <v>1365</v>
@@ -11368,7 +11368,7 @@
         <v>26</v>
       </c>
       <c r="E147">
-        <v>0.22215812499999998</v>
+        <v>0.28227150000000001</v>
       </c>
       <c r="F147">
         <v>1365</v>
@@ -11424,7 +11424,7 @@
         <v>16</v>
       </c>
       <c r="E148">
-        <v>0.24514000000000002</v>
+        <v>0.31147200000000003</v>
       </c>
       <c r="F148">
         <v>1365</v>
@@ -11760,7 +11760,7 @@
         <v>18</v>
       </c>
       <c r="E154">
-        <v>0.35238875000000003</v>
+        <v>0.44774100000000006</v>
       </c>
       <c r="F154">
         <v>1365</v>
@@ -11816,7 +11816,7 @@
         <v>26</v>
       </c>
       <c r="E155">
-        <v>0.26046124999999998</v>
+        <v>0.33093900000000004</v>
       </c>
       <c r="F155">
         <v>1365</v>
@@ -11872,7 +11872,7 @@
         <v>26</v>
       </c>
       <c r="E156">
-        <v>0.19534593749999996</v>
+        <v>0.24820425000000004</v>
       </c>
       <c r="F156">
         <v>1365</v>
@@ -11928,7 +11928,7 @@
         <v>73</v>
       </c>
       <c r="E157">
-        <v>0.24514000000000002</v>
+        <v>0.31147200000000003</v>
       </c>
       <c r="F157">
         <v>1365</v>
@@ -11984,7 +11984,7 @@
         <v>73</v>
       </c>
       <c r="E158">
-        <v>0.24514000000000002</v>
+        <v>0.31147200000000003</v>
       </c>
       <c r="F158">
         <v>1365</v>
@@ -12040,7 +12040,7 @@
         <v>73</v>
       </c>
       <c r="E159">
-        <v>0.22981874999999999</v>
+        <v>0.29200500000000001</v>
       </c>
       <c r="F159">
         <v>1365</v>
@@ -12096,7 +12096,7 @@
         <v>73</v>
       </c>
       <c r="E160">
-        <v>0.22981874999999999</v>
+        <v>0.29200500000000001</v>
       </c>
       <c r="F160">
         <v>1365</v>
@@ -12152,7 +12152,7 @@
         <v>14</v>
       </c>
       <c r="E161">
-        <v>0.22981874999999999</v>
+        <v>0.29200500000000001</v>
       </c>
       <c r="F161">
         <v>1365</v>
@@ -12208,7 +12208,7 @@
         <v>18</v>
       </c>
       <c r="E162">
-        <v>0.25280062500000006</v>
+        <v>0.32120550000000009</v>
       </c>
       <c r="F162">
         <v>1365</v>
@@ -12264,7 +12264,7 @@
         <v>73</v>
       </c>
       <c r="E163">
-        <v>0.24897031250000004</v>
+        <v>0.31633875000000006</v>
       </c>
       <c r="F163">
         <v>1365</v>
@@ -12320,7 +12320,7 @@
         <v>26</v>
       </c>
       <c r="E164">
-        <v>0.22215812499999998</v>
+        <v>0.28227150000000001</v>
       </c>
       <c r="F164">
         <v>1365</v>
@@ -12394,7 +12394,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1D2EBE5-809D-49AD-948E-AB257FD39CC8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3C9677C-D5E9-43FC-A703-E16EEAFEE64A}">
   <dimension ref="B9:T100"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -17442,7 +17442,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2434CFE9-D0F1-43C1-A23E-C4C7088C90B0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1F42391-C6DE-4677-855C-0628D03C7504}">
   <dimension ref="B9:T544"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -17527,7 +17527,7 @@
         <v>6.8000000000000005E-2</v>
       </c>
       <c r="G11">
-        <v>0.25389499999999998</v>
+        <v>0.32856999999999997</v>
       </c>
       <c r="H11">
         <v>4427.5</v>
@@ -17580,7 +17580,7 @@
         <v>8.5000000000000006E-2</v>
       </c>
       <c r="G12">
-        <v>0.23200749999999998</v>
+        <v>0.30024500000000004</v>
       </c>
       <c r="H12">
         <v>4427.5</v>
@@ -17633,7 +17633,7 @@
         <v>5.0999999999999997E-2</v>
       </c>
       <c r="G13">
-        <v>0.25389499999999998</v>
+        <v>0.32856999999999997</v>
       </c>
       <c r="H13">
         <v>4427.5</v>
@@ -17686,7 +17686,7 @@
         <v>5.8999999999999997E-2</v>
       </c>
       <c r="G14">
-        <v>0.25389499999999998</v>
+        <v>0.32856999999999997</v>
       </c>
       <c r="H14">
         <v>4427.5</v>
@@ -17739,7 +17739,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="G15">
-        <v>0.27140500000000001</v>
+        <v>0.35123000000000004</v>
       </c>
       <c r="H15">
         <v>4427.5</v>
@@ -17792,7 +17792,7 @@
         <v>4.1000000000000002E-2</v>
       </c>
       <c r="G16">
-        <v>0.20136499999999999</v>
+        <v>0.26059000000000004</v>
       </c>
       <c r="H16">
         <v>5197.5</v>
@@ -17845,7 +17845,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
       <c r="G17">
-        <v>0.24514000000000002</v>
+        <v>0.31724000000000008</v>
       </c>
       <c r="H17">
         <v>5197.5</v>
@@ -17898,7 +17898,7 @@
         <v>0.108</v>
       </c>
       <c r="G18">
-        <v>0.24514000000000002</v>
+        <v>0.31724000000000002</v>
       </c>
       <c r="H18">
         <v>5197.5</v>
@@ -17951,7 +17951,7 @@
         <v>1.5958305084745763</v>
       </c>
       <c r="G19">
-        <v>0.306425</v>
+        <v>0.39655000000000001</v>
       </c>
       <c r="H19">
         <v>3850.0000000000005</v>
@@ -18004,7 +18004,7 @@
         <v>0.03</v>
       </c>
       <c r="G20">
-        <v>0.26264999999999999</v>
+        <v>0.33990000000000004</v>
       </c>
       <c r="H20">
         <v>5197.5</v>
@@ -18057,7 +18057,7 @@
         <v>0.49149152542372881</v>
       </c>
       <c r="G21">
-        <v>0.306425</v>
+        <v>0.39655000000000001</v>
       </c>
       <c r="H21">
         <v>3850.0000000000005</v>
@@ -18110,7 +18110,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
       <c r="G22">
-        <v>0.24514000000000002</v>
+        <v>0.31724000000000008</v>
       </c>
       <c r="H22">
         <v>5197.5</v>
@@ -18163,7 +18163,7 @@
         <v>0.22450847457627116</v>
       </c>
       <c r="G23">
-        <v>0.28891500000000003</v>
+        <v>0.37389000000000006</v>
       </c>
       <c r="H23">
         <v>4427.5</v>
@@ -18216,7 +18216,7 @@
         <v>1.2681694915254238</v>
       </c>
       <c r="G24">
-        <v>0.306425</v>
+        <v>0.39655000000000001</v>
       </c>
       <c r="H24">
         <v>3850.0000000000005</v>
@@ -18269,7 +18269,7 @@
         <v>0.61803468208092449</v>
       </c>
       <c r="G25">
-        <v>0.2815455</v>
+        <v>0.36435300000000004</v>
       </c>
       <c r="N25" t="s">
         <v>387</v>
@@ -18310,7 +18310,7 @@
         <v>0.61803468208092449</v>
       </c>
       <c r="G26">
-        <v>0.2815455</v>
+        <v>0.36435300000000004</v>
       </c>
       <c r="N26" t="s">
         <v>387</v>
@@ -18351,7 +18351,7 @@
         <v>0.38393063583815007</v>
       </c>
       <c r="G27">
-        <v>0.2815455</v>
+        <v>0.36435299999999998</v>
       </c>
       <c r="N27" t="s">
         <v>387</v>
@@ -18392,7 +18392,7 @@
         <v>0.32</v>
       </c>
       <c r="G28">
-        <v>0.31518000000000002</v>
+        <v>0.40788000000000013</v>
       </c>
       <c r="H28">
         <v>2200</v>
@@ -18445,7 +18445,7 @@
         <v>0.32</v>
       </c>
       <c r="G29">
-        <v>0.31518000000000002</v>
+        <v>0.40788000000000013</v>
       </c>
       <c r="H29">
         <v>2200</v>
@@ -18498,7 +18498,7 @@
         <v>0.35</v>
       </c>
       <c r="G30">
-        <v>0.31518000000000002</v>
+        <v>0.40788000000000013</v>
       </c>
       <c r="H30">
         <v>2200</v>
@@ -18551,7 +18551,7 @@
         <v>0.24</v>
       </c>
       <c r="G31">
-        <v>0.28891500000000003</v>
+        <v>0.37389000000000006</v>
       </c>
       <c r="H31">
         <v>2530</v>
@@ -18604,7 +18604,7 @@
         <v>0.66</v>
       </c>
       <c r="G32">
-        <v>0.341445</v>
+        <v>0.44187000000000004</v>
       </c>
       <c r="H32">
         <v>2420</v>
@@ -18657,7 +18657,7 @@
         <v>0.66</v>
       </c>
       <c r="G33">
-        <v>0.341445</v>
+        <v>0.44187000000000004</v>
       </c>
       <c r="H33">
         <v>2420</v>
@@ -18710,7 +18710,7 @@
         <v>0.66</v>
       </c>
       <c r="G34">
-        <v>0.341445</v>
+        <v>0.44187000000000004</v>
       </c>
       <c r="H34">
         <v>2420</v>
@@ -18763,7 +18763,7 @@
         <v>0.66</v>
       </c>
       <c r="G35">
-        <v>0.36770999999999998</v>
+        <v>0.47586000000000006</v>
       </c>
       <c r="H35">
         <v>2640</v>
@@ -18816,7 +18816,7 @@
         <v>0.66</v>
       </c>
       <c r="G36">
-        <v>0.36770999999999998</v>
+        <v>0.47586000000000006</v>
       </c>
       <c r="H36">
         <v>2640</v>
@@ -18869,7 +18869,7 @@
         <v>0.66</v>
       </c>
       <c r="G37">
-        <v>0.36770999999999998</v>
+        <v>0.47586000000000006</v>
       </c>
       <c r="H37">
         <v>2640</v>
@@ -18922,7 +18922,7 @@
         <v>0.80800000000000005</v>
       </c>
       <c r="G38">
-        <v>0.47714750000000006</v>
+        <v>0.60625800000000007</v>
       </c>
       <c r="H38">
         <v>1100</v>
@@ -18975,7 +18975,7 @@
         <v>0.8</v>
       </c>
       <c r="G39">
-        <v>0.50778999999999996</v>
+        <v>0.64519199999999999</v>
       </c>
       <c r="H39">
         <v>1100</v>
@@ -19028,7 +19028,7 @@
         <v>0.23899999999999999</v>
       </c>
       <c r="G40">
-        <v>0.43774999999999997</v>
+        <v>0.55620000000000003</v>
       </c>
       <c r="H40">
         <v>1265</v>
@@ -19081,7 +19081,7 @@
         <v>0.8</v>
       </c>
       <c r="G41">
-        <v>0.50778999999999996</v>
+        <v>0.64519199999999999</v>
       </c>
       <c r="H41">
         <v>1100</v>
@@ -19134,7 +19134,7 @@
         <v>0.38100000000000001</v>
       </c>
       <c r="G42">
-        <v>0.4771475</v>
+        <v>0.60625800000000007</v>
       </c>
       <c r="H42">
         <v>1100</v>
@@ -19187,7 +19187,7 @@
         <v>0.38100000000000001</v>
       </c>
       <c r="G43">
-        <v>0.4771475</v>
+        <v>0.60625800000000007</v>
       </c>
       <c r="H43">
         <v>1100</v>
@@ -19240,7 +19240,7 @@
         <v>0.38100000000000001</v>
       </c>
       <c r="G44">
-        <v>0.4771475</v>
+        <v>0.60625800000000007</v>
       </c>
       <c r="H44">
         <v>1100</v>
@@ -19293,7 +19293,7 @@
         <v>0.40100000000000002</v>
       </c>
       <c r="G45">
-        <v>0.4771475</v>
+        <v>0.60625800000000007</v>
       </c>
       <c r="H45">
         <v>1100</v>
@@ -19346,7 +19346,7 @@
         <v>0.84799999999999998</v>
       </c>
       <c r="G46">
-        <v>0.4771475</v>
+        <v>0.60625800000000007</v>
       </c>
       <c r="H46">
         <v>1100</v>
@@ -19399,7 +19399,7 @@
         <v>0.40400000000000003</v>
       </c>
       <c r="G47">
-        <v>0.45963750000000003</v>
+        <v>0.58401000000000014</v>
       </c>
       <c r="H47">
         <v>1100</v>
@@ -19452,7 +19452,7 @@
         <v>0.753</v>
       </c>
       <c r="G48">
-        <v>0.47714749999999995</v>
+        <v>0.60625800000000007</v>
       </c>
       <c r="H48">
         <v>1100</v>
@@ -19505,7 +19505,7 @@
         <v>0.37</v>
       </c>
       <c r="G49">
-        <v>0.4771475</v>
+        <v>0.60625800000000007</v>
       </c>
       <c r="H49">
         <v>1100</v>
@@ -19558,7 +19558,7 @@
         <v>0.39</v>
       </c>
       <c r="G50">
-        <v>0.4771475</v>
+        <v>0.60625800000000007</v>
       </c>
       <c r="H50">
         <v>1100</v>
@@ -19611,7 +19611,7 @@
         <v>0.39</v>
       </c>
       <c r="G51">
-        <v>0.4771475</v>
+        <v>0.60625800000000007</v>
       </c>
       <c r="H51">
         <v>1100</v>
@@ -19664,7 +19664,7 @@
         <v>0.23</v>
       </c>
       <c r="G52">
-        <v>0.45526000000000005</v>
+        <v>0.57844800000000007</v>
       </c>
       <c r="H52">
         <v>1265</v>
@@ -19717,7 +19717,7 @@
         <v>0.39500000000000002</v>
       </c>
       <c r="G53">
-        <v>0.4771475</v>
+        <v>0.60625800000000007</v>
       </c>
       <c r="H53">
         <v>1100</v>
@@ -19770,7 +19770,7 @@
         <v>0.38100000000000001</v>
       </c>
       <c r="G54">
-        <v>0.4771475</v>
+        <v>0.60625800000000007</v>
       </c>
       <c r="H54">
         <v>1100</v>
@@ -19823,7 +19823,7 @@
         <v>0.42</v>
       </c>
       <c r="G55">
-        <v>0.4771475</v>
+        <v>0.60625800000000007</v>
       </c>
       <c r="H55">
         <v>1100</v>
@@ -19876,7 +19876,7 @@
         <v>0.42</v>
       </c>
       <c r="G56">
-        <v>0.4771475</v>
+        <v>0.60625800000000007</v>
       </c>
       <c r="H56">
         <v>1100</v>
@@ -19929,7 +19929,7 @@
         <v>0.38100000000000001</v>
       </c>
       <c r="G57">
-        <v>0.4771475</v>
+        <v>0.60625800000000007</v>
       </c>
       <c r="H57">
         <v>1100</v>
@@ -19982,7 +19982,7 @@
         <v>0.38100000000000001</v>
       </c>
       <c r="G58">
-        <v>0.4771475</v>
+        <v>0.60625800000000007</v>
       </c>
       <c r="H58">
         <v>1100</v>
@@ -20035,7 +20035,7 @@
         <v>0.38100000000000001</v>
       </c>
       <c r="G59">
-        <v>0.4771475</v>
+        <v>0.60625800000000007</v>
       </c>
       <c r="H59">
         <v>1100</v>
@@ -20088,7 +20088,7 @@
         <v>0.38100000000000001</v>
       </c>
       <c r="G60">
-        <v>0.4771475</v>
+        <v>0.60625800000000007</v>
       </c>
       <c r="H60">
         <v>1100</v>
@@ -20141,7 +20141,7 @@
         <v>0.34499999999999997</v>
       </c>
       <c r="G61">
-        <v>0.45963750000000003</v>
+        <v>0.58401000000000014</v>
       </c>
       <c r="H61">
         <v>1100</v>
@@ -20194,7 +20194,7 @@
         <v>0.33700000000000002</v>
       </c>
       <c r="G62">
-        <v>0.45963750000000003</v>
+        <v>0.58401000000000014</v>
       </c>
       <c r="H62">
         <v>1100</v>
@@ -20247,7 +20247,7 @@
         <v>0.38</v>
       </c>
       <c r="G63">
-        <v>0.47714749999999995</v>
+        <v>0.60625800000000007</v>
       </c>
       <c r="H63">
         <v>1100</v>
@@ -20300,7 +20300,7 @@
         <v>0.78</v>
       </c>
       <c r="G64">
-        <v>0.52529999999999999</v>
+        <v>0.66744000000000003</v>
       </c>
       <c r="H64">
         <v>1100</v>
@@ -20353,7 +20353,7 @@
         <v>0.76600000000000001</v>
       </c>
       <c r="G65">
-        <v>0.4771475</v>
+        <v>0.60625800000000007</v>
       </c>
       <c r="H65">
         <v>1100</v>
@@ -20406,7 +20406,7 @@
         <v>0.155</v>
       </c>
       <c r="G66">
-        <v>0.43774999999999997</v>
+        <v>0.55620000000000003</v>
       </c>
       <c r="H66">
         <v>1265</v>
@@ -20459,7 +20459,7 @@
         <v>0.8</v>
       </c>
       <c r="G67">
-        <v>0.4771475</v>
+        <v>0.60625800000000007</v>
       </c>
       <c r="H67">
         <v>1100</v>
@@ -20512,7 +20512,7 @@
         <v>0.4</v>
       </c>
       <c r="G68">
-        <v>0.4771475</v>
+        <v>0.60625800000000007</v>
       </c>
       <c r="H68">
         <v>1100</v>
@@ -20565,7 +20565,7 @@
         <v>0.38</v>
       </c>
       <c r="G69">
-        <v>0.47714749999999995</v>
+        <v>0.60625800000000007</v>
       </c>
       <c r="H69">
         <v>1100</v>
@@ -20618,7 +20618,7 @@
         <v>0.30499999999999999</v>
       </c>
       <c r="G70">
-        <v>0.45963749999999998</v>
+        <v>0.58401000000000014</v>
       </c>
       <c r="H70">
         <v>1100</v>
@@ -20671,7 +20671,7 @@
         <v>0.30499999999999999</v>
       </c>
       <c r="G71">
-        <v>0.45963749999999998</v>
+        <v>0.58401000000000014</v>
       </c>
       <c r="H71">
         <v>1100</v>
@@ -20724,7 +20724,7 @@
         <v>0.24</v>
       </c>
       <c r="G72">
-        <v>0.43774999999999997</v>
+        <v>0.55620000000000003</v>
       </c>
       <c r="H72">
         <v>1265</v>
@@ -20777,7 +20777,7 @@
         <v>0.24</v>
       </c>
       <c r="G73">
-        <v>0.43774999999999997</v>
+        <v>0.55620000000000003</v>
       </c>
       <c r="H73">
         <v>1265</v>
@@ -20830,7 +20830,7 @@
         <v>0.4</v>
       </c>
       <c r="G74">
-        <v>0.4771475</v>
+        <v>0.60625800000000007</v>
       </c>
       <c r="H74">
         <v>1100</v>
@@ -20883,7 +20883,7 @@
         <v>0.48</v>
       </c>
       <c r="G75">
-        <v>0.4771475</v>
+        <v>0.60625800000000007</v>
       </c>
       <c r="H75">
         <v>1100</v>
@@ -20936,7 +20936,7 @@
         <v>0.39200000000000002</v>
       </c>
       <c r="G76">
-        <v>0.4771475</v>
+        <v>0.60625800000000007</v>
       </c>
       <c r="H76">
         <v>1100</v>
@@ -20989,7 +20989,7 @@
         <v>0.38400000000000001</v>
       </c>
       <c r="G77">
-        <v>0.4771475</v>
+        <v>0.60625800000000007</v>
       </c>
       <c r="H77">
         <v>1100</v>
@@ -21042,7 +21042,7 @@
         <v>0.80600000000000005</v>
       </c>
       <c r="G78">
-        <v>0.4771475</v>
+        <v>0.60625800000000007</v>
       </c>
       <c r="H78">
         <v>1100</v>
@@ -21095,7 +21095,7 @@
         <v>0.36499999999999999</v>
       </c>
       <c r="G79">
-        <v>0.4771475</v>
+        <v>0.60625800000000007</v>
       </c>
       <c r="H79">
         <v>1100</v>
@@ -21148,7 +21148,7 @@
         <v>0.4</v>
       </c>
       <c r="G80">
-        <v>0.39397500000000002</v>
+        <v>0.50058000000000002</v>
       </c>
       <c r="H80">
         <v>1100</v>
@@ -21201,7 +21201,7 @@
         <v>0.35</v>
       </c>
       <c r="G81">
-        <v>0.47714749999999995</v>
+        <v>0.60625800000000007</v>
       </c>
       <c r="H81">
         <v>1100</v>
@@ -21254,7 +21254,7 @@
         <v>0.36799999999999999</v>
       </c>
       <c r="G82">
-        <v>0.4771475</v>
+        <v>0.60625800000000007</v>
       </c>
       <c r="H82">
         <v>1100</v>
@@ -21307,7 +21307,7 @@
         <v>0.36</v>
       </c>
       <c r="G83">
-        <v>0.4771475</v>
+        <v>0.60625800000000007</v>
       </c>
       <c r="H83">
         <v>1100</v>
@@ -21360,7 +21360,7 @@
         <v>0.38300000000000001</v>
       </c>
       <c r="G84">
-        <v>0.4771475</v>
+        <v>0.60625800000000007</v>
       </c>
       <c r="H84">
         <v>1100</v>
@@ -21413,7 +21413,7 @@
         <v>0.38400000000000001</v>
       </c>
       <c r="G85">
-        <v>0.4771475</v>
+        <v>0.60625800000000007</v>
       </c>
       <c r="H85">
         <v>1100</v>
@@ -21466,7 +21466,7 @@
         <v>0.38400000000000001</v>
       </c>
       <c r="G86">
-        <v>0.4771475</v>
+        <v>0.60625800000000007</v>
       </c>
       <c r="H86">
         <v>1100</v>
@@ -21519,7 +21519,7 @@
         <v>0.18</v>
       </c>
       <c r="G87">
-        <v>0.49028000000000005</v>
+        <v>0.62294400000000016</v>
       </c>
       <c r="H87">
         <v>1265</v>
@@ -21572,7 +21572,7 @@
         <v>0.38100000000000001</v>
       </c>
       <c r="G88">
-        <v>0.4771475</v>
+        <v>0.60625800000000007</v>
       </c>
       <c r="H88">
         <v>1100</v>
@@ -21625,7 +21625,7 @@
         <v>0.38100000000000001</v>
       </c>
       <c r="G89">
-        <v>0.4771475</v>
+        <v>0.60625800000000007</v>
       </c>
       <c r="H89">
         <v>1100</v>
@@ -21678,7 +21678,7 @@
         <v>0.42099999999999999</v>
       </c>
       <c r="G90">
-        <v>0.50778999999999996</v>
+        <v>0.64519199999999999</v>
       </c>
       <c r="H90">
         <v>1100</v>
@@ -21731,7 +21731,7 @@
         <v>0.39200000000000002</v>
       </c>
       <c r="G91">
-        <v>0.4771475</v>
+        <v>0.60625800000000007</v>
       </c>
       <c r="H91">
         <v>1100</v>
@@ -21784,7 +21784,7 @@
         <v>0.40699999999999997</v>
       </c>
       <c r="G92">
-        <v>0.47714749999999995</v>
+        <v>0.60625800000000007</v>
       </c>
       <c r="H92">
         <v>1100</v>
@@ -21837,7 +21837,7 @@
         <v>0.40699999999999997</v>
       </c>
       <c r="G93">
-        <v>0.47714749999999995</v>
+        <v>0.60625800000000007</v>
       </c>
       <c r="H93">
         <v>1100</v>
@@ -21890,7 +21890,7 @@
         <v>0.38500000000000001</v>
       </c>
       <c r="G94">
-        <v>0.4771475</v>
+        <v>0.60625800000000007</v>
       </c>
       <c r="H94">
         <v>1100</v>
@@ -21943,7 +21943,7 @@
         <v>0.76600000000000001</v>
       </c>
       <c r="G95">
-        <v>0.4771475</v>
+        <v>0.60625800000000007</v>
       </c>
       <c r="H95">
         <v>1100</v>
@@ -21996,7 +21996,7 @@
         <v>0.88500000000000001</v>
       </c>
       <c r="G96">
-        <v>0.4771475</v>
+        <v>0.60625800000000007</v>
       </c>
       <c r="H96">
         <v>1100</v>
@@ -22049,7 +22049,7 @@
         <v>0.38</v>
       </c>
       <c r="G97">
-        <v>0.47714749999999995</v>
+        <v>0.60625800000000007</v>
       </c>
       <c r="H97">
         <v>1100</v>
@@ -22102,7 +22102,7 @@
         <v>0.38</v>
       </c>
       <c r="G98">
-        <v>0.47714749999999995</v>
+        <v>0.60625800000000007</v>
       </c>
       <c r="H98">
         <v>1100</v>
@@ -22155,7 +22155,7 @@
         <v>0.76500000000000001</v>
       </c>
       <c r="G99">
-        <v>0.4771475</v>
+        <v>0.60625800000000007</v>
       </c>
       <c r="H99">
         <v>1100</v>
@@ -22208,7 +22208,7 @@
         <v>0.38500000000000001</v>
       </c>
       <c r="G100">
-        <v>0.4771475</v>
+        <v>0.60625800000000007</v>
       </c>
       <c r="H100">
         <v>1100</v>
@@ -22261,7 +22261,7 @@
         <v>0.78</v>
       </c>
       <c r="G101">
-        <v>0.4771475</v>
+        <v>0.60625800000000007</v>
       </c>
       <c r="H101">
         <v>1100</v>
@@ -22314,7 +22314,7 @@
         <v>0.76900000000000002</v>
       </c>
       <c r="G102">
-        <v>0.4771475</v>
+        <v>0.60625800000000007</v>
       </c>
       <c r="H102">
         <v>1100</v>
@@ -22367,7 +22367,7 @@
         <v>0.39500000000000002</v>
       </c>
       <c r="G103">
-        <v>0.50778999999999996</v>
+        <v>0.64519199999999999</v>
       </c>
       <c r="H103">
         <v>1100</v>
@@ -22420,7 +22420,7 @@
         <v>0.76</v>
       </c>
       <c r="G104">
-        <v>0.47714749999999995</v>
+        <v>0.60625800000000007</v>
       </c>
       <c r="H104">
         <v>1100</v>
@@ -22473,7 +22473,7 @@
         <v>0.38</v>
       </c>
       <c r="G105">
-        <v>0.47714749999999995</v>
+        <v>0.60625800000000007</v>
       </c>
       <c r="H105">
         <v>1100</v>
@@ -22526,7 +22526,7 @@
         <v>0.86699999999999999</v>
       </c>
       <c r="G106">
-        <v>0.4771475</v>
+        <v>0.60625800000000007</v>
       </c>
       <c r="H106">
         <v>1100</v>
@@ -22579,7 +22579,7 @@
         <v>0.85499999999999998</v>
       </c>
       <c r="G107">
-        <v>0.4771475</v>
+        <v>0.60625799999999996</v>
       </c>
       <c r="H107">
         <v>1100</v>
@@ -22632,7 +22632,7 @@
         <v>0.8</v>
       </c>
       <c r="G108">
-        <v>0.4771475</v>
+        <v>0.60625800000000007</v>
       </c>
       <c r="H108">
         <v>1100</v>
@@ -22685,7 +22685,7 @@
         <v>0.4</v>
       </c>
       <c r="G109">
-        <v>0.4771475</v>
+        <v>0.60625800000000007</v>
       </c>
       <c r="H109">
         <v>1100</v>
@@ -22738,7 +22738,7 @@
         <v>0.76500000000000001</v>
       </c>
       <c r="G110">
-        <v>0.52529999999999999</v>
+        <v>0.66744000000000003</v>
       </c>
       <c r="H110">
         <v>1100</v>
@@ -22791,7 +22791,7 @@
         <v>0.86</v>
       </c>
       <c r="G111">
-        <v>0.52529999999999999</v>
+        <v>0.66744000000000003</v>
       </c>
       <c r="H111">
         <v>1100</v>
@@ -22844,7 +22844,7 @@
         <v>0.43</v>
       </c>
       <c r="G112">
-        <v>0.52529999999999999</v>
+        <v>0.66744000000000003</v>
       </c>
       <c r="H112">
         <v>1100</v>
@@ -22897,7 +22897,7 @@
         <v>0.39300000000000002</v>
       </c>
       <c r="G113">
-        <v>0.4771475</v>
+        <v>0.60625800000000007</v>
       </c>
       <c r="H113">
         <v>1100</v>
@@ -22950,7 +22950,7 @@
         <v>0.38</v>
       </c>
       <c r="G114">
-        <v>0.47714749999999995</v>
+        <v>0.60625800000000007</v>
       </c>
       <c r="H114">
         <v>1100</v>
@@ -23003,7 +23003,7 @@
         <v>0.39200000000000002</v>
       </c>
       <c r="G115">
-        <v>0.4771475</v>
+        <v>0.60625800000000007</v>
       </c>
       <c r="H115">
         <v>1100</v>
@@ -23056,7 +23056,7 @@
         <v>0.80500000000000005</v>
       </c>
       <c r="G116">
-        <v>0.4771475</v>
+        <v>0.60625800000000007</v>
       </c>
       <c r="H116">
         <v>1100</v>
@@ -23109,7 +23109,7 @@
         <v>0.25600000000000001</v>
       </c>
       <c r="G117">
-        <v>0.43774999999999997</v>
+        <v>0.55620000000000003</v>
       </c>
       <c r="H117">
         <v>1265</v>
@@ -23162,7 +23162,7 @@
         <v>0.25600000000000001</v>
       </c>
       <c r="G118">
-        <v>0.43774999999999997</v>
+        <v>0.55620000000000003</v>
       </c>
       <c r="H118">
         <v>1265</v>
@@ -23215,7 +23215,7 @@
         <v>0.56399999999999995</v>
       </c>
       <c r="G119">
-        <v>0.45963750000000009</v>
+        <v>0.58401000000000014</v>
       </c>
       <c r="H119">
         <v>1100</v>
@@ -23268,7 +23268,7 @@
         <v>0.23</v>
       </c>
       <c r="G120">
-        <v>0.43774999999999997</v>
+        <v>0.55620000000000003</v>
       </c>
       <c r="H120">
         <v>1265</v>
@@ -23321,7 +23321,7 @@
         <v>0.57499999999999996</v>
       </c>
       <c r="G121">
-        <v>0.47714749999999995</v>
+        <v>0.60625800000000007</v>
       </c>
       <c r="H121">
         <v>1100</v>
@@ -23374,7 +23374,7 @@
         <v>0.26</v>
       </c>
       <c r="G122">
-        <v>0.45526000000000005</v>
+        <v>0.57844800000000007</v>
       </c>
       <c r="H122">
         <v>1265</v>
@@ -23427,7 +23427,7 @@
         <v>0.18</v>
       </c>
       <c r="G123">
-        <v>0.45526000000000005</v>
+        <v>0.57844800000000007</v>
       </c>
       <c r="H123">
         <v>1265</v>
@@ -23480,7 +23480,7 @@
         <v>0.4</v>
       </c>
       <c r="G124">
-        <v>0.4771475</v>
+        <v>0.60625800000000007</v>
       </c>
       <c r="H124">
         <v>1100</v>
@@ -23533,7 +23533,7 @@
         <v>4.8500000000000001E-2</v>
       </c>
       <c r="G125">
-        <v>0.47277000000000002</v>
+        <v>0.60069600000000012</v>
       </c>
       <c r="H125">
         <v>1485.0000000000002</v>
@@ -23586,7 +23586,7 @@
         <v>0.122</v>
       </c>
       <c r="G126">
-        <v>0.43774999999999997</v>
+        <v>0.55620000000000003</v>
       </c>
       <c r="H126">
         <v>1265</v>
@@ -23639,7 +23639,7 @@
         <v>0.125</v>
       </c>
       <c r="G127">
-        <v>0.43774999999999997</v>
+        <v>0.55620000000000003</v>
       </c>
       <c r="H127">
         <v>1265</v>
@@ -23692,7 +23692,7 @@
         <v>0.106</v>
       </c>
       <c r="G128">
-        <v>0.43774999999999997</v>
+        <v>0.55620000000000003</v>
       </c>
       <c r="H128">
         <v>1265</v>
@@ -23745,7 +23745,7 @@
         <v>8.7999999999999995E-2</v>
       </c>
       <c r="G129">
-        <v>0.43774999999999997</v>
+        <v>0.55620000000000003</v>
       </c>
       <c r="H129">
         <v>1265</v>
@@ -23798,7 +23798,7 @@
         <v>9.5000000000000001E-2</v>
       </c>
       <c r="G130">
-        <v>0.43774999999999997</v>
+        <v>0.55620000000000003</v>
       </c>
       <c r="H130">
         <v>1265</v>
@@ -23851,7 +23851,7 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="G131">
-        <v>0.45526000000000005</v>
+        <v>0.57844800000000007</v>
       </c>
       <c r="H131">
         <v>1265</v>
@@ -23904,7 +23904,7 @@
         <v>0.06</v>
       </c>
       <c r="G132">
-        <v>0.45526000000000005</v>
+        <v>0.57844800000000007</v>
       </c>
       <c r="H132">
         <v>1265</v>
@@ -23957,7 +23957,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
       <c r="G133">
-        <v>0.43775000000000003</v>
+        <v>0.55620000000000003</v>
       </c>
       <c r="H133">
         <v>1485.0000000000002</v>
@@ -24010,7 +24010,7 @@
         <v>0.20599999999999999</v>
       </c>
       <c r="G134">
-        <v>0.45526000000000005</v>
+        <v>0.57844800000000007</v>
       </c>
       <c r="H134">
         <v>1265</v>
@@ -24063,7 +24063,7 @@
         <v>4.3999999999999997E-2</v>
       </c>
       <c r="G135">
-        <v>0.47277000000000002</v>
+        <v>0.60069600000000012</v>
       </c>
       <c r="H135">
         <v>1485.0000000000002</v>
@@ -24116,7 +24116,7 @@
         <v>0.104</v>
       </c>
       <c r="G136">
-        <v>0.49028000000000005</v>
+        <v>0.62294400000000016</v>
       </c>
       <c r="H136">
         <v>1265</v>
@@ -24169,7 +24169,7 @@
         <v>9.9000000000000005E-2</v>
       </c>
       <c r="G137">
-        <v>0.45526000000000005</v>
+        <v>0.57844800000000007</v>
       </c>
       <c r="H137">
         <v>1265</v>
@@ -24222,7 +24222,7 @@
         <v>4.3999999999999997E-2</v>
       </c>
       <c r="G138">
-        <v>0.47277000000000002</v>
+        <v>0.60069600000000012</v>
       </c>
       <c r="H138">
         <v>1485.0000000000002</v>
@@ -24275,7 +24275,7 @@
         <v>0.14599999999999999</v>
       </c>
       <c r="G139">
-        <v>0.37646499999999999</v>
+        <v>0.47833199999999998</v>
       </c>
       <c r="H139">
         <v>1265</v>
@@ -24328,7 +24328,7 @@
         <v>5.3999999999999999E-2</v>
       </c>
       <c r="G140">
-        <v>0.43774999999999992</v>
+        <v>0.55620000000000003</v>
       </c>
       <c r="H140">
         <v>1265</v>
@@ -24381,7 +24381,7 @@
         <v>0.109</v>
       </c>
       <c r="G141">
-        <v>0.43774999999999997</v>
+        <v>0.55620000000000003</v>
       </c>
       <c r="H141">
         <v>1265</v>
@@ -24402,7 +24402,7 @@
         <v>150</v>
       </c>
       <c r="P141" t="s">
-        <v>512</v>
+        <v>397</v>
       </c>
       <c r="Q141" t="s">
         <v>389</v>
@@ -24434,7 +24434,7 @@
         <v>0.13700000000000001</v>
       </c>
       <c r="G142">
-        <v>0.43774999999999997</v>
+        <v>0.55620000000000003</v>
       </c>
       <c r="H142">
         <v>1265</v>
@@ -24455,7 +24455,7 @@
         <v>150</v>
       </c>
       <c r="P142" t="s">
-        <v>397</v>
+        <v>512</v>
       </c>
       <c r="Q142" t="s">
         <v>389</v>
@@ -24487,7 +24487,7 @@
         <v>0.05</v>
       </c>
       <c r="G143">
-        <v>0.42024</v>
+        <v>0.53395200000000009</v>
       </c>
       <c r="H143">
         <v>1485.0000000000002</v>
@@ -24540,7 +24540,7 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="G144">
-        <v>0.45526000000000005</v>
+        <v>0.57844800000000007</v>
       </c>
       <c r="H144">
         <v>1265</v>
@@ -24593,7 +24593,7 @@
         <v>0.36799999999999999</v>
       </c>
       <c r="G145">
-        <v>0.45526000000000011</v>
+        <v>0.57844800000000007</v>
       </c>
       <c r="H145">
         <v>1265</v>
@@ -24646,7 +24646,7 @@
         <v>0.05</v>
       </c>
       <c r="G146">
-        <v>0.43774999999999997</v>
+        <v>0.55620000000000003</v>
       </c>
       <c r="H146">
         <v>1485.0000000000002</v>
@@ -24699,7 +24699,7 @@
         <v>0.122</v>
       </c>
       <c r="G147">
-        <v>0.45526000000000005</v>
+        <v>0.57844800000000007</v>
       </c>
       <c r="H147">
         <v>1265</v>
@@ -24752,7 +24752,7 @@
         <v>0.13500000000000001</v>
       </c>
       <c r="G148">
-        <v>0.45526000000000011</v>
+        <v>0.57844800000000007</v>
       </c>
       <c r="H148">
         <v>1265</v>
@@ -24805,7 +24805,7 @@
         <v>6.2E-2</v>
       </c>
       <c r="G149">
-        <v>0.49028000000000005</v>
+        <v>0.62294400000000016</v>
       </c>
       <c r="H149">
         <v>1265</v>
@@ -24858,7 +24858,7 @@
         <v>0.8</v>
       </c>
       <c r="G150">
-        <v>0.28891500000000003</v>
+        <v>0.36709200000000008</v>
       </c>
       <c r="H150">
         <v>880.00000000000011</v>
@@ -24911,7 +24911,7 @@
         <v>0.15</v>
       </c>
       <c r="G151">
-        <v>0.28016000000000002</v>
+        <v>0.35596800000000001</v>
       </c>
       <c r="H151">
         <v>1012</v>
@@ -24964,7 +24964,7 @@
         <v>0.15</v>
       </c>
       <c r="G152">
-        <v>0.28016000000000002</v>
+        <v>0.35596800000000001</v>
       </c>
       <c r="H152">
         <v>1012</v>
@@ -25017,7 +25017,7 @@
         <v>0.35599999999999998</v>
       </c>
       <c r="G153">
-        <v>0.24076250000000005</v>
+        <v>0.30591000000000007</v>
       </c>
       <c r="H153">
         <v>880.00000000000011</v>
@@ -25070,7 +25070,7 @@
         <v>0.248</v>
       </c>
       <c r="G154">
-        <v>0.23200750000000001</v>
+        <v>0.29478600000000005</v>
       </c>
       <c r="H154">
         <v>1012</v>
@@ -25123,7 +25123,7 @@
         <v>0.112</v>
       </c>
       <c r="G155">
-        <v>0.23200750000000001</v>
+        <v>0.29478600000000005</v>
       </c>
       <c r="H155">
         <v>1012</v>
@@ -25176,7 +25176,7 @@
         <v>0.112</v>
       </c>
       <c r="G156">
-        <v>0.23200750000000001</v>
+        <v>0.29478600000000005</v>
       </c>
       <c r="H156">
         <v>1012</v>
@@ -25229,7 +25229,7 @@
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="G157">
-        <v>0.24514</v>
+        <v>0.31147200000000008</v>
       </c>
       <c r="H157">
         <v>1188</v>
@@ -25282,7 +25282,7 @@
         <v>0.10779999999999999</v>
       </c>
       <c r="G158">
-        <v>0.21887499999999999</v>
+        <v>0.27810000000000001</v>
       </c>
       <c r="H158">
         <v>1012</v>
@@ -25335,7 +25335,7 @@
         <v>0.10779999999999999</v>
       </c>
       <c r="G159">
-        <v>0.21887499999999999</v>
+        <v>0.27810000000000001</v>
       </c>
       <c r="H159">
         <v>1012</v>
@@ -25388,7 +25388,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="G160">
-        <v>0.22325249999999996</v>
+        <v>0.28366200000000003</v>
       </c>
       <c r="H160">
         <v>1188</v>
@@ -25441,7 +25441,7 @@
         <v>0.08</v>
       </c>
       <c r="G161">
-        <v>0.27140500000000001</v>
+        <v>0.34484400000000004</v>
       </c>
       <c r="H161">
         <v>1012</v>
@@ -25494,7 +25494,7 @@
         <v>0.03</v>
       </c>
       <c r="G162">
-        <v>0.21012</v>
+        <v>0.26697600000000005</v>
       </c>
       <c r="H162">
         <v>1188</v>
@@ -25547,7 +25547,7 @@
         <v>0.05</v>
       </c>
       <c r="G163">
-        <v>0.22325249999999999</v>
+        <v>0.28366200000000003</v>
       </c>
       <c r="H163">
         <v>1188</v>
@@ -25600,7 +25600,7 @@
         <v>0.05</v>
       </c>
       <c r="G164">
-        <v>0.24514000000000002</v>
+        <v>0.31147200000000008</v>
       </c>
       <c r="H164">
         <v>1188</v>
@@ -25653,7 +25653,7 @@
         <v>0.05</v>
       </c>
       <c r="G165">
-        <v>0.24514000000000002</v>
+        <v>0.31147200000000008</v>
       </c>
       <c r="H165">
         <v>1188</v>
@@ -25706,7 +25706,7 @@
         <v>0.05</v>
       </c>
       <c r="G166">
-        <v>0.26264999999999999</v>
+        <v>0.33372000000000002</v>
       </c>
       <c r="H166">
         <v>1188</v>
@@ -25759,7 +25759,7 @@
         <v>0.05</v>
       </c>
       <c r="G167">
-        <v>0.26264999999999999</v>
+        <v>0.33372000000000002</v>
       </c>
       <c r="H167">
         <v>1188</v>
@@ -25812,7 +25812,7 @@
         <v>2.5500502305884107</v>
       </c>
       <c r="G168">
-        <v>0.2815455</v>
+        <v>0.35772840000000006</v>
       </c>
       <c r="N168" t="s">
         <v>387</v>
@@ -25853,7 +25853,7 @@
         <v>2.9907347651207039</v>
       </c>
       <c r="G169">
-        <v>0.2815455</v>
+        <v>0.35772840000000006</v>
       </c>
       <c r="N169" t="s">
         <v>387</v>
@@ -25894,7 +25894,7 @@
         <v>1.2982809611581656</v>
       </c>
       <c r="G170">
-        <v>0.2815455</v>
+        <v>0.35772840000000006</v>
       </c>
       <c r="N170" t="s">
         <v>387</v>
@@ -25935,7 +25935,7 @@
         <v>0.2630164695347188</v>
       </c>
       <c r="G171">
-        <v>0.2815455</v>
+        <v>0.35772840000000006</v>
       </c>
       <c r="N171" t="s">
         <v>387</v>
@@ -25976,7 +25976,7 @@
         <v>4.6857175735979988</v>
       </c>
       <c r="G172">
-        <v>0.2815455</v>
+        <v>0.35772840000000006</v>
       </c>
       <c r="N172" t="s">
         <v>387</v>
@@ -26017,7 +26017,7 @@
         <v>4.3999999999999997E-2</v>
       </c>
       <c r="G173">
-        <v>0.28891500000000003</v>
+        <v>0.36709200000000008</v>
       </c>
       <c r="H173">
         <v>1633.5000000000002</v>
@@ -26070,7 +26070,7 @@
         <v>7.3999999999999996E-2</v>
       </c>
       <c r="G174">
-        <v>0.31518000000000002</v>
+        <v>0.40046400000000004</v>
       </c>
       <c r="H174">
         <v>1391.5</v>
@@ -26123,7 +26123,7 @@
         <v>7.5200000000000003E-2</v>
       </c>
       <c r="G175">
-        <v>0.31518000000000002</v>
+        <v>0.40046400000000004</v>
       </c>
       <c r="H175">
         <v>1391.5</v>
@@ -26176,7 +26176,7 @@
         <v>2.46E-2</v>
       </c>
       <c r="G176">
-        <v>0.31080249999999998</v>
+        <v>0.39490200000000003</v>
       </c>
       <c r="H176">
         <v>1633.5000000000002</v>
@@ -26229,7 +26229,7 @@
         <v>5.8000000000000003E-2</v>
       </c>
       <c r="G177">
-        <v>0.31518000000000002</v>
+        <v>0.40046400000000004</v>
       </c>
       <c r="H177">
         <v>1391.5</v>
@@ -26282,7 +26282,7 @@
         <v>0.112</v>
       </c>
       <c r="G178">
-        <v>0.31517999999999996</v>
+        <v>0.40046400000000004</v>
       </c>
       <c r="H178">
         <v>1482.25</v>
@@ -26335,7 +26335,7 @@
         <v>3.15E-2</v>
       </c>
       <c r="G179">
-        <v>0.28891500000000003</v>
+        <v>0.36709200000000008</v>
       </c>
       <c r="H179">
         <v>1633.5000000000002</v>
@@ -26388,7 +26388,7 @@
         <v>7.3599999999999999E-2</v>
       </c>
       <c r="G180">
-        <v>0.31518000000000002</v>
+        <v>0.40046400000000004</v>
       </c>
       <c r="H180">
         <v>1391.5</v>
@@ -26441,7 +26441,7 @@
         <v>0.108</v>
       </c>
       <c r="G181">
-        <v>0.31518000000000002</v>
+        <v>0.40046399999999999</v>
       </c>
       <c r="H181">
         <v>1391.5</v>
@@ -26494,7 +26494,7 @@
         <v>0.16</v>
       </c>
       <c r="G182">
-        <v>0.27140500000000001</v>
+        <v>0.34484400000000004</v>
       </c>
       <c r="H182">
         <v>1518.0000000000002</v>
@@ -26547,7 +26547,7 @@
         <v>0.16</v>
       </c>
       <c r="G183">
-        <v>0.27140500000000001</v>
+        <v>0.34484400000000004</v>
       </c>
       <c r="H183">
         <v>1518.0000000000002</v>
@@ -26600,7 +26600,7 @@
         <v>0.16</v>
       </c>
       <c r="G184">
-        <v>0.27140500000000001</v>
+        <v>0.34484400000000004</v>
       </c>
       <c r="H184">
         <v>1518.0000000000002</v>
@@ -26653,7 +26653,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="G185">
-        <v>0.26264999999999999</v>
+        <v>0.33372000000000002</v>
       </c>
       <c r="H185">
         <v>1518.0000000000002</v>
@@ -26706,7 +26706,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="G186">
-        <v>0.27140500000000001</v>
+        <v>0.34484400000000004</v>
       </c>
       <c r="H186">
         <v>1518.0000000000002</v>
@@ -26759,7 +26759,7 @@
         <v>0.02</v>
       </c>
       <c r="G187">
-        <v>0.29329250000000001</v>
+        <v>0.37265400000000004</v>
       </c>
       <c r="H187">
         <v>1782.0000000000005</v>
@@ -26812,7 +26812,7 @@
         <v>6.0999999999999999E-2</v>
       </c>
       <c r="G188">
-        <v>0.25389499999999998</v>
+        <v>0.32259599999999999</v>
       </c>
       <c r="H188">
         <v>1782.0000000000002</v>
@@ -26865,7 +26865,7 @@
         <v>3.1E-2</v>
       </c>
       <c r="G189">
-        <v>0.26264999999999999</v>
+        <v>0.33372000000000002</v>
       </c>
       <c r="H189">
         <v>1782.0000000000002</v>
@@ -26918,7 +26918,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
       <c r="G190">
-        <v>0.27140500000000001</v>
+        <v>0.34484400000000004</v>
       </c>
       <c r="H190">
         <v>1782.0000000000002</v>
@@ -26971,7 +26971,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G191">
-        <v>0.28016000000000002</v>
+        <v>0.35596800000000001</v>
       </c>
       <c r="H191">
         <v>1518.0000000000002</v>
@@ -32016,7 +32016,7 @@
         <v>314</v>
       </c>
       <c r="P288" t="s">
-        <v>512</v>
+        <v>397</v>
       </c>
       <c r="Q288" t="s">
         <v>389</v>
@@ -32069,7 +32069,7 @@
         <v>314</v>
       </c>
       <c r="P289" t="s">
-        <v>397</v>
+        <v>512</v>
       </c>
       <c r="Q289" t="s">
         <v>389</v>
@@ -32228,7 +32228,7 @@
         <v>319</v>
       </c>
       <c r="P292" t="s">
-        <v>397</v>
+        <v>512</v>
       </c>
       <c r="Q292" t="s">
         <v>389</v>
@@ -32281,7 +32281,7 @@
         <v>319</v>
       </c>
       <c r="P293" t="s">
-        <v>512</v>
+        <v>397</v>
       </c>
       <c r="Q293" t="s">
         <v>389</v>
@@ -32493,7 +32493,7 @@
         <v>326</v>
       </c>
       <c r="P297" t="s">
-        <v>512</v>
+        <v>397</v>
       </c>
       <c r="Q297" t="s">
         <v>389</v>
@@ -32546,7 +32546,7 @@
         <v>326</v>
       </c>
       <c r="P298" t="s">
-        <v>397</v>
+        <v>512</v>
       </c>
       <c r="Q298" t="s">
         <v>389</v>
@@ -32864,7 +32864,7 @@
         <v>336</v>
       </c>
       <c r="P304" t="s">
-        <v>512</v>
+        <v>397</v>
       </c>
       <c r="Q304" t="s">
         <v>389</v>
@@ -32917,7 +32917,7 @@
         <v>336</v>
       </c>
       <c r="P305" t="s">
-        <v>397</v>
+        <v>512</v>
       </c>
       <c r="Q305" t="s">
         <v>389</v>
@@ -33585,7 +33585,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
       <c r="G318">
-        <v>0.40273000000000003</v>
+        <v>0.51170400000000005</v>
       </c>
       <c r="H318">
         <v>1633.5000000000002</v>
@@ -33638,7 +33638,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
       <c r="G319">
-        <v>0.28016000000000002</v>
+        <v>0.35596800000000001</v>
       </c>
       <c r="H319">
         <v>1633.5000000000002</v>
@@ -33691,7 +33691,7 @@
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="G320">
-        <v>0.29766999999999999</v>
+        <v>0.37821600000000005</v>
       </c>
       <c r="H320">
         <v>1391.5</v>
@@ -33744,7 +33744,7 @@
         <v>0.18</v>
       </c>
       <c r="G321">
-        <v>0.22325249999999996</v>
+        <v>0.28366200000000003</v>
       </c>
       <c r="H321">
         <v>1138.5</v>
@@ -33797,7 +33797,7 @@
         <v>0.32</v>
       </c>
       <c r="G322">
-        <v>0.28016000000000002</v>
+        <v>0.35596800000000001</v>
       </c>
       <c r="H322">
         <v>1430.0000000000002</v>
@@ -33850,7 +33850,7 @@
         <v>0.32</v>
       </c>
       <c r="G323">
-        <v>0.28016000000000002</v>
+        <v>0.35596800000000001</v>
       </c>
       <c r="H323">
         <v>1430.0000000000002</v>
@@ -33903,7 +33903,7 @@
         <v>0.16</v>
       </c>
       <c r="G324">
-        <v>0.26264999999999999</v>
+        <v>0.33372000000000002</v>
       </c>
       <c r="H324">
         <v>1644.4999999999995</v>
@@ -33956,7 +33956,7 @@
         <v>0.16</v>
       </c>
       <c r="G325">
-        <v>0.26264999999999999</v>
+        <v>0.33372000000000002</v>
       </c>
       <c r="H325">
         <v>1644.4999999999995</v>
@@ -34009,7 +34009,7 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="G326">
-        <v>0.26264999999999999</v>
+        <v>0.33372000000000002</v>
       </c>
       <c r="H326">
         <v>1644.4999999999998</v>
@@ -34062,7 +34062,7 @@
         <v>8.1000000000000003E-2</v>
       </c>
       <c r="G327">
-        <v>0.27140500000000001</v>
+        <v>0.34484400000000004</v>
       </c>
       <c r="H327">
         <v>1644.4999999999995</v>
@@ -34115,7 +34115,7 @@
         <v>0.1</v>
       </c>
       <c r="G328">
-        <v>0.28891500000000003</v>
+        <v>0.36709200000000008</v>
       </c>
       <c r="H328">
         <v>1644.4999999999998</v>
@@ -34168,7 +34168,7 @@
         <v>0.21</v>
       </c>
       <c r="G329">
-        <v>0.25389499999999998</v>
+        <v>0.32259599999999999</v>
       </c>
       <c r="H329">
         <v>1644.4999999999998</v>
@@ -34221,7 +34221,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="G330">
-        <v>0.28453750000000005</v>
+        <v>0.36153000000000007</v>
       </c>
       <c r="H330">
         <v>1930.5000000000002</v>
@@ -34274,7 +34274,7 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="G331">
-        <v>0.25389499999999998</v>
+        <v>0.32259599999999999</v>
       </c>
       <c r="H331">
         <v>1644.4999999999998</v>
@@ -37059,7 +37059,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L411">
-        <v>0.17863101551144786</v>
+        <v>0.17863101551144783</v>
       </c>
     </row>
     <row r="412" spans="2:12" x14ac:dyDescent="0.45">
@@ -37082,7 +37082,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L412">
-        <v>0.17863101551144786</v>
+        <v>0.17863101551144783</v>
       </c>
     </row>
     <row r="413" spans="2:12" x14ac:dyDescent="0.45">
@@ -37105,7 +37105,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L413">
-        <v>0.17863101551144786</v>
+        <v>0.17863101551144783</v>
       </c>
     </row>
     <row r="414" spans="2:12" x14ac:dyDescent="0.45">
@@ -41699,7 +41699,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F6418C2-14AD-4171-9ADC-1D8A944F58BC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9B2D32F-4D46-4016-803A-3A9E40DC2D72}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_ITA_grids_syn_5/vt_vervestacks_ITA_v1.xlsx
+++ b/VerveStacks_ITA_grids_syn_5/vt_vervestacks_ITA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids_syn_5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{578732B1-3B90-40BA-8427-D6262BABA8CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A6CFC287-84DB-434F-8798-CA8A17F203BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{AE05CA47-5B9F-4601-9462-9953F0A10C4A}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{49464E81-DE25-405A-B09B-CAD3E224A90E}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -3673,7 +3673,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5084EAA3-681C-4254-95F9-B8D6D567783B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4CEADEB-B6D6-4353-9A40-FFE4B89ED59C}">
   <dimension ref="B9:T165"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -11062,7 +11062,7 @@
         <v>935</v>
       </c>
       <c r="P141" t="s">
-        <v>1067</v>
+        <v>1077</v>
       </c>
       <c r="Q141" t="s">
         <v>389</v>
@@ -11118,7 +11118,7 @@
         <v>935</v>
       </c>
       <c r="P142" t="s">
-        <v>1077</v>
+        <v>1067</v>
       </c>
       <c r="Q142" t="s">
         <v>389</v>
@@ -12394,7 +12394,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3C9677C-D5E9-43FC-A703-E16EEAFEE64A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1B7EECC-1D62-4F33-8C0E-CB5D25D57832}">
   <dimension ref="B9:T100"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -17442,7 +17442,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1F42391-C6DE-4677-855C-0628D03C7504}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3996CE24-9189-4ABE-9E83-6089507C43A9}">
   <dimension ref="B9:T544"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24402,7 +24402,7 @@
         <v>150</v>
       </c>
       <c r="P141" t="s">
-        <v>397</v>
+        <v>512</v>
       </c>
       <c r="Q141" t="s">
         <v>389</v>
@@ -24455,7 +24455,7 @@
         <v>150</v>
       </c>
       <c r="P142" t="s">
-        <v>512</v>
+        <v>397</v>
       </c>
       <c r="Q142" t="s">
         <v>389</v>
@@ -32016,7 +32016,7 @@
         <v>314</v>
       </c>
       <c r="P288" t="s">
-        <v>397</v>
+        <v>512</v>
       </c>
       <c r="Q288" t="s">
         <v>389</v>
@@ -32069,7 +32069,7 @@
         <v>314</v>
       </c>
       <c r="P289" t="s">
-        <v>512</v>
+        <v>397</v>
       </c>
       <c r="Q289" t="s">
         <v>389</v>
@@ -32228,7 +32228,7 @@
         <v>319</v>
       </c>
       <c r="P292" t="s">
-        <v>512</v>
+        <v>397</v>
       </c>
       <c r="Q292" t="s">
         <v>389</v>
@@ -32281,7 +32281,7 @@
         <v>319</v>
       </c>
       <c r="P293" t="s">
-        <v>397</v>
+        <v>512</v>
       </c>
       <c r="Q293" t="s">
         <v>389</v>
@@ -32493,7 +32493,7 @@
         <v>326</v>
       </c>
       <c r="P297" t="s">
-        <v>397</v>
+        <v>512</v>
       </c>
       <c r="Q297" t="s">
         <v>389</v>
@@ -32546,7 +32546,7 @@
         <v>326</v>
       </c>
       <c r="P298" t="s">
-        <v>512</v>
+        <v>397</v>
       </c>
       <c r="Q298" t="s">
         <v>389</v>
@@ -32864,7 +32864,7 @@
         <v>336</v>
       </c>
       <c r="P304" t="s">
-        <v>397</v>
+        <v>512</v>
       </c>
       <c r="Q304" t="s">
         <v>389</v>
@@ -32917,7 +32917,7 @@
         <v>336</v>
       </c>
       <c r="P305" t="s">
-        <v>512</v>
+        <v>397</v>
       </c>
       <c r="Q305" t="s">
         <v>389</v>
@@ -32970,7 +32970,7 @@
         <v>337</v>
       </c>
       <c r="P306" t="s">
-        <v>397</v>
+        <v>512</v>
       </c>
       <c r="Q306" t="s">
         <v>389</v>
@@ -33023,7 +33023,7 @@
         <v>337</v>
       </c>
       <c r="P307" t="s">
-        <v>512</v>
+        <v>397</v>
       </c>
       <c r="Q307" t="s">
         <v>389</v>
@@ -33712,7 +33712,7 @@
         <v>363</v>
       </c>
       <c r="P320" t="s">
-        <v>397</v>
+        <v>512</v>
       </c>
       <c r="Q320" t="s">
         <v>389</v>
@@ -33765,7 +33765,7 @@
         <v>363</v>
       </c>
       <c r="P321" t="s">
-        <v>512</v>
+        <v>397</v>
       </c>
       <c r="Q321" t="s">
         <v>389</v>
@@ -34330,7 +34330,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L332">
-        <v>0.20827624154866115</v>
+        <v>0.20827624154866126</v>
       </c>
     </row>
     <row r="333" spans="2:20" x14ac:dyDescent="0.45">
@@ -34353,7 +34353,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L333">
-        <v>0.20827624154866115</v>
+        <v>0.20827624154866126</v>
       </c>
     </row>
     <row r="334" spans="2:20" x14ac:dyDescent="0.45">
@@ -34376,7 +34376,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L334">
-        <v>0.20827624154866115</v>
+        <v>0.20827624154866126</v>
       </c>
     </row>
     <row r="335" spans="2:20" x14ac:dyDescent="0.45">
@@ -41699,7 +41699,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9B2D32F-4D46-4016-803A-3A9E40DC2D72}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB616BF5-FDFC-47C4-A105-BB97F7CBE6D2}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_ITA_grids_syn_5/vt_vervestacks_ITA_v1.xlsx
+++ b/VerveStacks_ITA_grids_syn_5/vt_vervestacks_ITA_v1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids_syn_5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A6CFC287-84DB-434F-8798-CA8A17F203BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5B15DFF9-560D-444F-A762-E72CC3379BD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{49464E81-DE25-405A-B09B-CAD3E224A90E}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{4D4C7ADD-D139-4B9C-A42B-1C31CE7BAEBB}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -3673,7 +3673,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4CEADEB-B6D6-4353-9A40-FFE4B89ED59C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D41593B-76ED-4A0C-A083-7C255DE492BC}">
   <dimension ref="B9:T165"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -11062,7 +11062,7 @@
         <v>935</v>
       </c>
       <c r="P141" t="s">
-        <v>1077</v>
+        <v>1067</v>
       </c>
       <c r="Q141" t="s">
         <v>389</v>
@@ -11118,7 +11118,7 @@
         <v>935</v>
       </c>
       <c r="P142" t="s">
-        <v>1067</v>
+        <v>1077</v>
       </c>
       <c r="Q142" t="s">
         <v>389</v>
@@ -12394,7 +12394,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1B7EECC-1D62-4F33-8C0E-CB5D25D57832}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07286B33-8E1E-4C08-BE4C-9144AA87DC53}">
   <dimension ref="B9:T100"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -17442,7 +17442,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3996CE24-9189-4ABE-9E83-6089507C43A9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C87089E1-F7F2-4753-A510-9D2B0D2D4835}">
   <dimension ref="B9:T544"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24402,7 +24402,7 @@
         <v>150</v>
       </c>
       <c r="P141" t="s">
-        <v>512</v>
+        <v>397</v>
       </c>
       <c r="Q141" t="s">
         <v>389</v>
@@ -24455,7 +24455,7 @@
         <v>150</v>
       </c>
       <c r="P142" t="s">
-        <v>397</v>
+        <v>512</v>
       </c>
       <c r="Q142" t="s">
         <v>389</v>
@@ -32016,7 +32016,7 @@
         <v>314</v>
       </c>
       <c r="P288" t="s">
-        <v>512</v>
+        <v>397</v>
       </c>
       <c r="Q288" t="s">
         <v>389</v>
@@ -32069,7 +32069,7 @@
         <v>314</v>
       </c>
       <c r="P289" t="s">
-        <v>397</v>
+        <v>512</v>
       </c>
       <c r="Q289" t="s">
         <v>389</v>
@@ -32228,7 +32228,7 @@
         <v>319</v>
       </c>
       <c r="P292" t="s">
-        <v>397</v>
+        <v>512</v>
       </c>
       <c r="Q292" t="s">
         <v>389</v>
@@ -32281,7 +32281,7 @@
         <v>319</v>
       </c>
       <c r="P293" t="s">
-        <v>512</v>
+        <v>397</v>
       </c>
       <c r="Q293" t="s">
         <v>389</v>
@@ -32493,7 +32493,7 @@
         <v>326</v>
       </c>
       <c r="P297" t="s">
-        <v>512</v>
+        <v>397</v>
       </c>
       <c r="Q297" t="s">
         <v>389</v>
@@ -32546,7 +32546,7 @@
         <v>326</v>
       </c>
       <c r="P298" t="s">
-        <v>397</v>
+        <v>512</v>
       </c>
       <c r="Q298" t="s">
         <v>389</v>
@@ -32599,7 +32599,7 @@
         <v>328</v>
       </c>
       <c r="P299" t="s">
-        <v>512</v>
+        <v>397</v>
       </c>
       <c r="Q299" t="s">
         <v>389</v>
@@ -32652,7 +32652,7 @@
         <v>328</v>
       </c>
       <c r="P300" t="s">
-        <v>397</v>
+        <v>512</v>
       </c>
       <c r="Q300" t="s">
         <v>389</v>
@@ -32970,7 +32970,7 @@
         <v>337</v>
       </c>
       <c r="P306" t="s">
-        <v>512</v>
+        <v>397</v>
       </c>
       <c r="Q306" t="s">
         <v>389</v>
@@ -33023,7 +33023,7 @@
         <v>337</v>
       </c>
       <c r="P307" t="s">
-        <v>397</v>
+        <v>512</v>
       </c>
       <c r="Q307" t="s">
         <v>389</v>
@@ -33712,7 +33712,7 @@
         <v>363</v>
       </c>
       <c r="P320" t="s">
-        <v>512</v>
+        <v>397</v>
       </c>
       <c r="Q320" t="s">
         <v>389</v>
@@ -33765,7 +33765,7 @@
         <v>363</v>
       </c>
       <c r="P321" t="s">
-        <v>397</v>
+        <v>512</v>
       </c>
       <c r="Q321" t="s">
         <v>389</v>
@@ -33818,7 +33818,7 @@
         <v>365</v>
       </c>
       <c r="P322" t="s">
-        <v>512</v>
+        <v>397</v>
       </c>
       <c r="Q322" t="s">
         <v>389</v>
@@ -33871,7 +33871,7 @@
         <v>365</v>
       </c>
       <c r="P323" t="s">
-        <v>397</v>
+        <v>512</v>
       </c>
       <c r="Q323" t="s">
         <v>389</v>
@@ -34330,7 +34330,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L332">
-        <v>0.20827624154866126</v>
+        <v>0.20827624154866117</v>
       </c>
     </row>
     <row r="333" spans="2:20" x14ac:dyDescent="0.45">
@@ -34353,7 +34353,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L333">
-        <v>0.20827624154866126</v>
+        <v>0.20827624154866117</v>
       </c>
     </row>
     <row r="334" spans="2:20" x14ac:dyDescent="0.45">
@@ -34376,7 +34376,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L334">
-        <v>0.20827624154866126</v>
+        <v>0.20827624154866117</v>
       </c>
     </row>
     <row r="335" spans="2:20" x14ac:dyDescent="0.45">
@@ -37059,7 +37059,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L411">
-        <v>0.17863101551144783</v>
+        <v>0.17863101551144786</v>
       </c>
     </row>
     <row r="412" spans="2:12" x14ac:dyDescent="0.45">
@@ -37082,7 +37082,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L412">
-        <v>0.17863101551144783</v>
+        <v>0.17863101551144786</v>
       </c>
     </row>
     <row r="413" spans="2:12" x14ac:dyDescent="0.45">
@@ -37105,7 +37105,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L413">
-        <v>0.17863101551144783</v>
+        <v>0.17863101551144786</v>
       </c>
     </row>
     <row r="414" spans="2:12" x14ac:dyDescent="0.45">
@@ -41699,7 +41699,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB616BF5-FDFC-47C4-A105-BB97F7CBE6D2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A761C86-FF34-4703-8F45-7DBC42735F4A}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_ITA_grids_syn_5/vt_vervestacks_ITA_v1.xlsx
+++ b/VerveStacks_ITA_grids_syn_5/vt_vervestacks_ITA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids_syn_5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{46FAC66B-F8CB-4F36-A965-884FC1E079A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6A1BA8B3-F5DA-4035-890C-A85E53D65F9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{E42AE662-8987-4C50-B6FE-ADF8063CFB5A}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{F23A8B99-E6D8-4B29-B900-08BFF4E56EDF}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -3658,7 +3658,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6E2C025-31B3-4254-B52F-A39381330670}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADD3438F-45F7-4DF7-BF1D-E5EA5E18E8A3}">
   <dimension ref="B9:T157"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -11931,7 +11931,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFD3759A-4475-4AAD-98F8-5D0840F67931}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EE7B40E-D212-41C3-9605-17AC716C4822}">
   <dimension ref="B9:T100"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -16979,7 +16979,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C82AF61-3448-4FBB-A8F9-D5BF1339171D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{560F5695-8F58-4133-8FFF-681B08C3B85A}">
   <dimension ref="B9:T549"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24160,7 +24160,7 @@
         <v>154</v>
       </c>
       <c r="P145" t="s">
-        <v>520</v>
+        <v>402</v>
       </c>
       <c r="Q145" t="s">
         <v>394</v>
@@ -24213,7 +24213,7 @@
         <v>154</v>
       </c>
       <c r="P146" t="s">
-        <v>402</v>
+        <v>520</v>
       </c>
       <c r="Q146" t="s">
         <v>394</v>
@@ -32387,7 +32387,7 @@
         <v>332</v>
       </c>
       <c r="P303" t="s">
-        <v>520</v>
+        <v>402</v>
       </c>
       <c r="Q303" t="s">
         <v>394</v>
@@ -32440,7 +32440,7 @@
         <v>332</v>
       </c>
       <c r="P304" t="s">
-        <v>402</v>
+        <v>520</v>
       </c>
       <c r="Q304" t="s">
         <v>394</v>
@@ -32652,7 +32652,7 @@
         <v>340</v>
       </c>
       <c r="P308" t="s">
-        <v>520</v>
+        <v>402</v>
       </c>
       <c r="Q308" t="s">
         <v>394</v>
@@ -32705,7 +32705,7 @@
         <v>340</v>
       </c>
       <c r="P309" t="s">
-        <v>402</v>
+        <v>520</v>
       </c>
       <c r="Q309" t="s">
         <v>394</v>
@@ -33500,7 +33500,7 @@
         <v>367</v>
       </c>
       <c r="P324" t="s">
-        <v>402</v>
+        <v>520</v>
       </c>
       <c r="Q324" t="s">
         <v>394</v>
@@ -33553,7 +33553,7 @@
         <v>367</v>
       </c>
       <c r="P325" t="s">
-        <v>520</v>
+        <v>402</v>
       </c>
       <c r="Q325" t="s">
         <v>394</v>
@@ -33606,7 +33606,7 @@
         <v>369</v>
       </c>
       <c r="P326" t="s">
-        <v>520</v>
+        <v>402</v>
       </c>
       <c r="Q326" t="s">
         <v>394</v>
@@ -33659,7 +33659,7 @@
         <v>369</v>
       </c>
       <c r="P327" t="s">
-        <v>402</v>
+        <v>520</v>
       </c>
       <c r="Q327" t="s">
         <v>394</v>
@@ -41561,7 +41561,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2127C076-AEBF-446C-8FB5-36060F222312}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF820D02-9A20-469C-9EE4-E65A92ED19C1}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_ITA_grids_syn_5/vt_vervestacks_ITA_v1.xlsx
+++ b/VerveStacks_ITA_grids_syn_5/vt_vervestacks_ITA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids_syn_5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6A1BA8B3-F5DA-4035-890C-A85E53D65F9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{79628477-C34E-4734-97C7-76EA09D307EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{F23A8B99-E6D8-4B29-B900-08BFF4E56EDF}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{35CEB0BF-3C9E-4A44-AD10-B3C24A77F031}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -3658,7 +3658,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADD3438F-45F7-4DF7-BF1D-E5EA5E18E8A3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAC7AE39-08C5-414A-9E47-790CF3B34F8E}">
   <dimension ref="B9:T157"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -11931,7 +11931,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EE7B40E-D212-41C3-9605-17AC716C4822}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66C588C0-108D-4F0D-BFB6-7AC1EB42C394}">
   <dimension ref="B9:T100"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -16979,7 +16979,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{560F5695-8F58-4133-8FFF-681B08C3B85A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BB54FF2-3190-4CDA-80AE-B3D3EF0F2A48}">
   <dimension ref="B9:T549"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24160,7 +24160,7 @@
         <v>154</v>
       </c>
       <c r="P145" t="s">
-        <v>402</v>
+        <v>520</v>
       </c>
       <c r="Q145" t="s">
         <v>394</v>
@@ -24213,7 +24213,7 @@
         <v>154</v>
       </c>
       <c r="P146" t="s">
-        <v>520</v>
+        <v>402</v>
       </c>
       <c r="Q146" t="s">
         <v>394</v>
@@ -32387,7 +32387,7 @@
         <v>332</v>
       </c>
       <c r="P303" t="s">
-        <v>402</v>
+        <v>520</v>
       </c>
       <c r="Q303" t="s">
         <v>394</v>
@@ -32440,7 +32440,7 @@
         <v>332</v>
       </c>
       <c r="P304" t="s">
-        <v>520</v>
+        <v>402</v>
       </c>
       <c r="Q304" t="s">
         <v>394</v>
@@ -33500,7 +33500,7 @@
         <v>367</v>
       </c>
       <c r="P324" t="s">
-        <v>520</v>
+        <v>402</v>
       </c>
       <c r="Q324" t="s">
         <v>394</v>
@@ -33553,7 +33553,7 @@
         <v>367</v>
       </c>
       <c r="P325" t="s">
-        <v>402</v>
+        <v>520</v>
       </c>
       <c r="Q325" t="s">
         <v>394</v>
@@ -41561,7 +41561,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF820D02-9A20-469C-9EE4-E65A92ED19C1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC7CB9F4-7385-4AF8-8A1B-86636D2D3C63}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
